--- a/セリフ編集/キャラタイプ別/ヤンキー×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/ヤンキー×ノーマル.xlsx
@@ -328,7 +328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H297"/>
+  <dimension ref="A1:H316"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1922,7 +1922,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.normal.delinquent[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.delinquent[1]</t>
+          <t xml:space="preserve">ahead.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1947,14 +1947,14 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちくしょう……覚えてろ……！</t>
+          <t xml:space="preserve">片付いた話を蒸し返すな。……いい加減、疲れるんだよ</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.normal.delinquent[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.delinquent[1]</t>
+          <t xml:space="preserve">behind.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1979,14 +1979,14 @@
       </c>
       <c r="F51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わりだ。もう目の前に現れるな</t>
+          <t xml:space="preserve">終わった扱いされんのが、一番腹立つんだよ</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.normal.delinquent[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="12">
@@ -2011,14 +2011,14 @@
       </c>
       <c r="F52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたけどよ……清々しいぜ。お前が相手で良かった</t>
+          <t xml:space="preserve">ちくしょう……覚えてろ……！</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.normal.delinquent[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="12">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="F53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お前がいたから強くなれた。……サンキュな</t>
+          <t xml:space="preserve">終わりだ。もう目の前に現れるな</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal.delinquent[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2060,12 +2060,12 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.delinquent[1]</t>
+          <t xml:space="preserve">loser.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2075,14 +2075,14 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げ場はねえ。ここで終わりだ</t>
+          <t xml:space="preserve">負けたけどよ……清々しいぜ。お前が相手で良かった</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal.delinquent[2]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.delinquent[2]</t>
+          <t xml:space="preserve">winner.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2107,14 +2107,14 @@
       </c>
       <c r="F55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てめえとの因縁、今夜ぶった斬る</t>
+          <t xml:space="preserve">お前がいたから強くなれた。……サンキュな</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.delinquent[1]</t>
+          <t xml:space="preserve">attacker.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2139,14 +2139,14 @@
       </c>
       <c r="F56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来いよ。返り討ちにしてやる</t>
+          <t xml:space="preserve">逃げ場はねえ。ここで終わりだ</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal.delinquent[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.delinquent[2]</t>
+          <t xml:space="preserve">attacker.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2171,14 +2171,14 @@
       </c>
       <c r="F57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">打てるもんなら打ってみろ</t>
+          <t xml:space="preserve">てめえとの因縁、今夜ぶった斬る</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.delinquent[1]</t>
+          <t xml:space="preserve">defender.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2203,14 +2203,14 @@
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ずっと待ってた。この日を</t>
+          <t xml:space="preserve">来いよ。返り討ちにしてやる</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.delinquent[1]</t>
+          <t xml:space="preserve">defender.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2235,14 +2235,14 @@
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ああ。来いよ</t>
+          <t xml:space="preserve">打てるもんなら打ってみろ</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="12">
@@ -2267,14 +2267,14 @@
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日で終わりだ。覚悟しろ</t>
+          <t xml:space="preserve">……ずっと待ってた。この日を</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal.delinquent[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.delinquent[2]</t>
+          <t xml:space="preserve">defender.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっ倒してやるよ、今夜な</t>
+          <t xml:space="preserve">……ああ。来いよ</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.delinquent[1]</t>
+          <t xml:space="preserve">attacker.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2331,14 +2331,14 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等だ。来いよ</t>
+          <t xml:space="preserve">今日で終わりだ。覚悟しろ</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal.delinquent[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.delinquent[2]</t>
+          <t xml:space="preserve">attacker.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2363,14 +2363,14 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やれるもんならやってみな</t>
+          <t xml:space="preserve">ぶっ倒してやるよ、今夜な</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.normal.delinquent[1]</t>
+          <t xml:space="preserve">defender.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2395,14 +2395,14 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">長かったな……今日で終わりだ</t>
+          <t xml:space="preserve">上等だ。来いよ</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.normal.delinquent[1]</t>
+          <t xml:space="preserve">defender.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2427,14 +2427,14 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ああ。最高の終わりにしようぜ</t>
+          <t xml:space="preserve">やれるもんならやってみな</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.delinquent[1]</t>
+          <t xml:space="preserve">fateAttacker.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2459,14 +2459,14 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ……次は絶対ぶっ倒す</t>
+          <t xml:space="preserve">長かったな……今日で終わりだ</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.delinquent[1]</t>
+          <t xml:space="preserve">fateDefender.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次もぶっ倒す。覚えとけ</t>
+          <t xml:space="preserve">ああ。最高の終わりにしようぜ</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.normal.delinquent[1]</t>
+          <t xml:space="preserve">loserLines.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2523,14 +2523,14 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…敵わなかった。…でもよ、まだ終わってねえぞ</t>
+          <t xml:space="preserve">くそっ……次は絶対ぶっ倒す</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2540,12 +2540,12 @@
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.normal.delinquent[1]</t>
+          <t xml:space="preserve">winnerLines.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2555,14 +2555,14 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと…一つ決着がついた…でもよ、なんかまだ胸がざわつくんだ</t>
+          <t xml:space="preserve">次もぶっ倒す。覚えとけ</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.delinquent[1]</t>
+          <t xml:space="preserve">fateLoser.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2587,14 +2587,14 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…負けた。…でもこれで終わりだと思うなよ</t>
+          <t xml:space="preserve">くそっ…敵わなかった。…でもよ、まだ終わってねえぞ</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.delinquent[1]</t>
+          <t xml:space="preserve">fateWinner.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2619,14 +2619,14 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ひとまず決着だ…でも、なんだろ。まだモヤモヤすんな</t>
+          <t xml:space="preserve">やっと…一つ決着がついた…でもよ、なんかまだ胸がざわつくんだ</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.delinquent[1]</t>
+          <t xml:space="preserve">loser.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2651,14 +2651,14 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ……ありえねえ……！</t>
+          <t xml:space="preserve">くそっ…負けた。…でもこれで終わりだと思うなよ</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.delinquent[1]</t>
+          <t xml:space="preserve">winner.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2683,14 +2683,14 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうだ……！ これが俺の答えだ！</t>
+          <t xml:space="preserve">ひとまず決着だ…でも、なんだろ。まだモヤモヤすんな</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.normal.delinquent[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.normal.delinquent[1]</t>
+          <t xml:space="preserve">loserLines.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2715,14 +2715,14 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が{nameA}を睨みつけた。「……てめえがそう来るなら、こっちも容赦しねえぞ」</t>
+          <t xml:space="preserve">くそっ……ありえねえ……！</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.lose[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2732,29 +2732,29 @@
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.lose[1]</t>
+          <t xml:space="preserve">winnerLines.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました。……すんません、社長。</t>
+          <t xml:space="preserve">どうだ……！ これが俺の答えだ！</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.lose[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2764,29 +2764,29 @@
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.lose[2]</t>
+          <t xml:space="preserve">awakening.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">だめでした。悔しいっす、正直。</t>
+          <t xml:space="preserve">{nameB}が{nameA}を睨みつけた。「……てめえがそう来るなら、こっちも容赦しねえぞ」</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.lose[1]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.lose[3]</t>
+          <t xml:space="preserve">delinquent_normal.lose[1]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr" s="2">
@@ -2811,14 +2811,14 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てませんでした。……次は絶対返します。</t>
+          <t xml:space="preserve">負けました。……すんません、社長。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.petition[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.lose[2]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.petition[1]</t>
+          <t xml:space="preserve">delinquent_normal.lose[2]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="2">
@@ -2843,14 +2843,14 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あの人とやらせてください。</t>
+          <t xml:space="preserve">だめでした。悔しいっす、正直。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.petition[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.lose[3]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.petition[2]</t>
+          <t xml:space="preserve">delinquent_normal.lose[3]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="2">
@@ -2875,14 +2875,14 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お願いがあるんすよ。あの人と当ててほしい。</t>
+          <t xml:space="preserve">勝てませんでした。……次は絶対返します。</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.petition[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.petition[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.petition[3]</t>
+          <t xml:space="preserve">delinquent_normal.petition[1]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="2">
@@ -2907,14 +2907,14 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと引っかかってる相手がいる。組ませてください。</t>
+          <t xml:space="preserve">社長、あの人とやらせてください。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.sendoff[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.petition[2]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.sendoff[1]</t>
+          <t xml:space="preserve">delinquent_normal.petition[2]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
@@ -2939,14 +2939,14 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。行ってきます。</t>
+          <t xml:space="preserve">お願いがあるんすよ。あの人と当ててほしい。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.sendoff[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.petition[3]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.sendoff[2]</t>
+          <t xml:space="preserve">delinquent_normal.petition[3]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
@@ -2971,14 +2971,14 @@
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジっすか。……あざす、社長。</t>
+          <t xml:space="preserve">ずっと引っかかってる相手がいる。組ませてください。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.sendoff[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.sendoff[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.sendoff[3]</t>
+          <t xml:space="preserve">delinquent_normal.sendoff[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -3003,14 +3003,14 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">恩に着ます。ちゃんと結果出してきます。</t>
+          <t xml:space="preserve">ありがとうございます。行ってきます。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.sendoff[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.win[1]</t>
+          <t xml:space="preserve">delinquent_normal.sendoff[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3035,14 +3035,14 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。ありがとうございました。</t>
+          <t xml:space="preserve">マジっすか。……あざす、社長。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.sendoff[3]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.win[2]</t>
+          <t xml:space="preserve">delinquent_normal.sendoff[3]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3067,14 +3067,14 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ってきたっす。頷いてくれたおかげで。</t>
+          <t xml:space="preserve">恩に着ます。ちゃんと結果出してきます。</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.win[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.win[3]</t>
+          <t xml:space="preserve">delinquent_normal.win[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3099,14 +3099,14 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい報告持ってきました。勝ちです。</t>
+          <t xml:space="preserve">勝ちました。ありがとうございました。</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal._accept[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.win[2]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal._accept[1]</t>
+          <t xml:space="preserve">delinquent_normal.win[2]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3131,14 +3131,14 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、指名されて逃げる趣味はねぇよ。</t>
+          <t xml:space="preserve">勝ってきたっす。頷いてくれたおかげで。</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal._accept[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.delinquent_normal.win[3]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal._accept[2]</t>
+          <t xml:space="preserve">delinquent_normal.win[3]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3163,14 +3163,14 @@
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいっすよ、受けて立つ。</t>
+          <t xml:space="preserve">いい報告持ってきました。勝ちです。</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal._accept[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal._accept[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal._accept[3]</t>
+          <t xml:space="preserve">delinquent_normal._accept[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3195,14 +3195,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そう来たか。分かった、やろうぜ。</t>
+          <t xml:space="preserve">まあ、指名されて逃げる趣味はねぇよ。</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.draw[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal._accept[2]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.draw[1]</t>
+          <t xml:space="preserve">delinquent_normal._accept[2]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3227,14 +3227,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分けか。すっきりしねぇな。</t>
+          <t xml:space="preserve">いいっすよ、受けて立つ。</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.draw[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal._accept[3]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.draw[2]</t>
+          <t xml:space="preserve">delinquent_normal._accept[3]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3259,14 +3259,14 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着つかずって、一番モヤるやつだ。</t>
+          <t xml:space="preserve">そう来たか。分かった、やろうぜ。</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.draw[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.draw[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.draw[3]</t>
+          <t xml:space="preserve">delinquent_normal.draw[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3291,14 +3291,14 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、悪い試合じゃなかったっす。</t>
+          <t xml:space="preserve">決まらなかったか。すっきりしねぇな。</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.lose[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.draw[2]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.lose[1]</t>
+          <t xml:space="preserve">delinquent_normal.draw[2]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3323,14 +3323,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けだ。ちゃんと認めるよ。</t>
+          <t xml:space="preserve">決着つかずって、一番モヤるやつだ。</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.lose[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.draw[3]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.lose[2]</t>
+          <t xml:space="preserve">delinquent_normal.draw[3]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3355,14 +3355,14 @@
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそ、届かなかったか。次は分かんねぇぞ。</t>
+          <t xml:space="preserve">まあ、悪い試合じゃなかったっす。</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.lose[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.lose[3]</t>
+          <t xml:space="preserve">delinquent_normal.lose[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3387,14 +3387,14 @@
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたの勝ち。文句なしだ。</t>
+          <t xml:space="preserve">……負けだ。ちゃんと認めるよ。</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.lose[2]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.win[1]</t>
+          <t xml:space="preserve">delinquent_normal.lose[2]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3419,14 +3419,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受けて正解だったな。それだけだ。</t>
+          <t xml:space="preserve">くそ、届かなかったか。次は分かんねぇぞ。</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.lose[3]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.win[2]</t>
+          <t xml:space="preserve">delinquent_normal.lose[3]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3451,14 +3451,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんた強かったよ。でも今日はこっちだ。</t>
+          <t xml:space="preserve">あんたの勝ち。文句なしだ。</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.win[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent_normal.win[3]</t>
+          <t xml:space="preserve">delinquent_normal.win[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3483,14 +3483,14 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悪ぃな。譲れねぇもんがあってさ。</t>
+          <t xml:space="preserve">受けて正解だったな。それだけだ。</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.win[2]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3500,29 +3500,29 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent_normal.win[2]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかった。もうちょっとだけやってみるか</t>
+          <t xml:space="preserve">あんた強かったよ。でも今日はこっちだ。</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.delinquent_normal.win[3]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3532,29 +3532,29 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent_normal.win[3]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少しだけだ…あのベルトにもう一回手を伸ばしてーんだ</t>
+          <t xml:space="preserve">悪ぃな。譲れねぇもんがあってさ。</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.normal.delinquent[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.normal.delinquent[1]</t>
+          <t xml:space="preserve">accepted.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3579,14 +3579,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ使い道があるってか。いいぜ、付き合ってやるよ</t>
+          <t xml:space="preserve">…いろいろ世話になった。向こうでも闘い続けるよ</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.normal.delinquent[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.normal.delinquent[1]</t>
+          <t xml:space="preserve">accepted.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お前がそう言うなら…もうちょっとだけやってみるか</t>
+          <t xml:space="preserve">ここで過ごした日々は忘れねえ</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.normal.delinquent[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.normal.delinquent[1]</t>
+          <t xml:space="preserve">defended.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3643,14 +3643,14 @@
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後にいい試合させてくれよ。それだけでいい</t>
+          <t xml:space="preserve">…ここに残れて、ほっとしたよ</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.normal.delinquent[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.normal.delinquent[1]</t>
+          <t xml:space="preserve">defended.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3675,14 +3675,14 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言われなくても辞めるつもりだったっつーの</t>
+          <t xml:space="preserve">社長…ありがとな。期待には応えるからさ</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.normal.delinquent[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.normal.delinquent[1]</t>
+          <t xml:space="preserve">defense_failed.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3707,14 +3707,14 @@
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかったよ。潮時ってやつだろ</t>
+          <t xml:space="preserve">…悪い。新しい場所で答えを出すよ</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal.delinquent[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.normal.delinquent[1]</t>
+          <t xml:space="preserve">defense_failed.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3739,14 +3739,14 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかってるよ。もう限界なんだろ</t>
+          <t xml:space="preserve">世話になった。…またどっかでな</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.normal.delinquent[1]</t>
+          <t xml:space="preserve">default.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3771,14 +3771,14 @@
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかってたよ。もう追いつけねーって</t>
+          <t xml:space="preserve">…わかった。もうちょっとだけやってみるか</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3788,12 +3788,12 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.normal.delinquent[1]</t>
+          <t xml:space="preserve">former_champ.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3803,14 +3803,14 @@
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンに引退しろだと？ ふざけんな</t>
+          <t xml:space="preserve">もう少しだけだ…あのベルトにもう一回手を伸ばしてーんだ</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.normal.delinquent[1]</t>
+          <t xml:space="preserve">heel.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3835,14 +3835,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">追い出す気かよ。そう簡単にいくと思うなよ</t>
+          <t xml:space="preserve">まだ使い道があるってか。いいぜ、付き合ってやるよ</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.normal.delinquent[1]</t>
+          <t xml:space="preserve">high_trust.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3867,14 +3867,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わんねーよ。あたしはまだ闘える</t>
+          <t xml:space="preserve">お前がそう言うなら…もうちょっとだけやってみるか</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.normal.delinquent[1]</t>
+          <t xml:space="preserve">accept_former_champ.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3899,14 +3899,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引退だと？ 次の興行見てろ。後悔させてやる</t>
+          <t xml:space="preserve">最後にいい試合させてくれよ。それだけでいい</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3916,12 +3916,12 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.normal.delinquent[1]</t>
+          <t xml:space="preserve">accept_heel.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3931,14 +3931,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点からの景色、忘れねーよ</t>
+          <t xml:space="preserve">言われなくても辞めるつもりだったっつーの</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.normal.delinquent[1]</t>
+          <t xml:space="preserve">accept_no_title.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3963,14 +3963,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトには届かなかった。でもよ、後悔はねーよ</t>
+          <t xml:space="preserve">…わかったよ。潮時ってやつだろ</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.normal.delinquent[1]</t>
+          <t xml:space="preserve">accept_terminal.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3995,14 +3995,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">泣いてんじゃねーよ。みっともねーな</t>
+          <t xml:space="preserve">…わかってるよ。もう限界なんだろ</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.normal.delinquent[1]</t>
+          <t xml:space="preserve">accept_winless.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4027,14 +4027,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが全部だった。嘘じゃねーよ</t>
+          <t xml:space="preserve">…わかってたよ。もう追いつけねーって</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.normal.delinquent[1]</t>
+          <t xml:space="preserve">refuse_champ.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4059,14 +4059,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ何もやってねーのに…嘘だろ…</t>
+          <t xml:space="preserve">チャンピオンに引退しろだと？ ふざけんな</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.normal.delinquent[1]</t>
+          <t xml:space="preserve">refuse_distrust.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4091,14 +4091,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体がよ…もう言うこと聞かねーんだ…</t>
+          <t xml:space="preserve">追い出す気かよ。そう簡単にいくと思うなよ</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.normal.delinquent[1]</t>
+          <t xml:space="preserve">refuse_fighting.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4123,14 +4123,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わかってたよ。いつか来るってな</t>
+          <t xml:space="preserve">まだ終わんねーよ。あたしはまだ闘える</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.normal.delinquent[1]</t>
+          <t xml:space="preserve">refuse_heel.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4155,14 +4155,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルト…まだ返したくなかったんだよ…</t>
+          <t xml:space="preserve">引退だと？ 次の興行見てろ。後悔させてやる</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">A1_champion.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4187,14 +4187,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どこにも行かねーよ。ここが一番おもしれーからな</t>
+          <t xml:space="preserve">頂点からの景色、忘れねーよ</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4204,29 +4204,29 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.normal.delinquent[1]</t>
+          <t xml:space="preserve">A2_uncrowned.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">サンキュ、社長。ちゃんと働くからよ。</t>
+          <t xml:space="preserve">ベルトには届かなかった。でもよ、後悔はねーよ</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4236,29 +4236,29 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.normal.delinquent[1]</t>
+          <t xml:space="preserve">A3_heel.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まー上がるだけマシか。サンキュ。</t>
+          <t xml:space="preserve">泣いてんじゃねーよ。みっともねーな</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4268,29 +4268,29 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.normal.delinquent[1]</t>
+          <t xml:space="preserve">A4_veteran.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……チッ。まあ分かったよ。</t>
+          <t xml:space="preserve">ここが全部だった。嘘じゃねーよ</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4300,29 +4300,29 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.normal.delinquent[1]</t>
+          <t xml:space="preserve">B1_young.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ちょっといいか。{tenure}{record}給料の話なんだけどさ。もうちょい出してくんねーの？</t>
+          <t xml:space="preserve">まだ何もやってねーのに…嘘だろ…</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4332,29 +4332,29 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.normal.delinquent[1]</t>
+          <t xml:space="preserve">B2_prime.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……マジかよ。……まあいいけどさ。</t>
+          <t xml:space="preserve">体がよ…もう言うこと聞かねーんだ…</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4364,29 +4364,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.normal.delinquent[1]</t>
+          <t xml:space="preserve">B3_older.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">聞いてくれんのか。{record}正直、もっと面白えとこでやりてーんだよ。</t>
+          <t xml:space="preserve">わかってたよ。いつか来るってな</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4396,29 +4396,29 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.normal.delinquent[1]</t>
+          <t xml:space="preserve">B4_champion_injury.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}悪いけど、もうここ出るわ。</t>
+          <t xml:space="preserve">このベルト…まだ返したくなかったんだよ…</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.normal.delinquent[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4428,29 +4428,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……おう。{tenure_farewell}{rivalry}じゃーな。</t>
+          <t xml:space="preserve">どこにも行かねーよ。ここが一番おもしれーからな</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.normal.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.normal.delinquent[1]</t>
+          <t xml:space="preserve">raise_accept.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4475,14 +4475,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪いけど、もう決めたんだよ。気持ちは変わらねー。</t>
+          <t xml:space="preserve">サンキュ、社長。ちゃんと働くからよ。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.normal.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.normal.delinquent[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4507,476 +4507,476 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……マジかよ。そこまで言うなら、もうちょいいてやるか。</t>
+          <t xml:space="preserve">まー上がるだけマシか。サンキュ。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_negotiate_refuse.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……チッ。まあ分かったよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_open.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、ちょっといいか。{tenure}{record}給料の話なんだけどさ。もうちょい出してくんねーの？</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_refuse.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……マジかよ。……まあいいけどさ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、話は手短にするっす。辞めます。もう決めました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">世話になりました。でも、もうここじゃ続けられないっす。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">聞いてくれんのか。{record}正直、もっと面白えとこでやりてーんだよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}悪いけど、もうここ出るわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……おう。{tenure_farewell}{rivalry}じゃーな。</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……悪いけど、もう決めたんだよ。気持ちは変わらねー。</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……マジかよ。そこまで言うなら、もうちょいいてやるか。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.normal.delinquent[1]</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr" s="2">
+      <c r="B141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr" s="12">
+      <c r="D141" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.normal.delinquent[1]</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr" s="2">
+      <c r="E141" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr" s="3">
+      <c r="F141" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">悪いな、話を聞く気にならねぇ。
 今の仲間を裏切るわけにはいかねぇから</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="40" customHeight="1">
-      <c r="A132" t="inlineStr" s="15">
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.normal.delinquent[1]</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr" s="2">
+      <c r="B142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr" s="12">
+      <c r="D142" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.normal.delinquent[1]</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr" s="2">
+      <c r="E142" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr" s="3">
+      <c r="F142" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">悪ぃけど、今回はパスだ。
 縁があればまたな</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="40" customHeight="1">
-      <c r="A133" t="inlineStr" s="15">
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.normal.delinquent[1]</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr" s="2">
+      <c r="B143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr" s="12">
+      <c r="D143" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.normal.delinquent[1]</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr" s="2">
+      <c r="E143" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr" s="3">
+      <c r="F143" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">あたしを引き抜くってか？
 …条件次第だな</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="40" customHeight="1">
-      <c r="A134" t="inlineStr" s="15">
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.normal.delinquent[1]</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr" s="2">
+      <c r="B144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr" s="12">
+      <c r="D144" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.normal.delinquent[1]</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr" s="2">
+      <c r="E144" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr" s="3">
+      <c r="F144" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…わかった、行くぜ。
 実力で居場所作ってやるよ</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="40" customHeight="1">
-      <c r="A135" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">黙ってたけど、もう限界だっつーの。</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="40" customHeight="1">
-      <c r="A136" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">おっしゃ！ なんか壁越えた気がするぜ！</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="40" customHeight="1">
-      <c r="A137" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES.normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">（…なんだ、この感覚。体が勝手に動きやがる——）</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="40" customHeight="1">
-      <c r="A138" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cap_reached.normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…ちっ、ここが天井か。でも悪くねえ</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="40" customHeight="1">
-      <c r="A139" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_elite.normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ここまで来たら、もう誰にも止められねえ</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="40" customHeight="1">
-      <c r="A140" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_growth.normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">おっ、ちょっとは強くなったじゃん</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="40" customHeight="1">
-      <c r="A141" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_legend.normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">はは…マジかよ、こんなとこまで来ちまった</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="40" customHeight="1">
-      <c r="A142" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">pop_growth.normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">おっ、知名度上がってんじゃん</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="40" customHeight="1">
-      <c r="A143" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">pop_star.normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">すっげえ声援だな…やべえ、ちょっと鳥肌立った</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="40" customHeight="1">
-      <c r="A144" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">何のために闘ってんだよ…もうわかんねー</t>
-        </is>
-      </c>
-    </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
@@ -4986,19 +4986,19 @@
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだやれる…やってやるよ</t>
+          <t xml:space="preserve">黙ってたけど、もう限界だっつーの。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
@@ -5023,14 +5023,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと…やっと戻ってこれたぜ</t>
+          <t xml:space="preserve">おっしゃ！ なんか壁越えた気がするぜ！</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.delinquent[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5055,14 +5055,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの負けから…何かおかしいんだよ</t>
+          <t xml:space="preserve">（…なんだ、この感覚。体が勝手に動きやがる——）</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.normal.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.normal.delinquent[1]</t>
+          <t xml:space="preserve">cap_reached.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5087,14 +5087,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は治ったはずだろ…なんで動けねーんだ</t>
+          <t xml:space="preserve">…ちっ、ここが天井か。でも悪くねえ</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.normal.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.normal.delinquent[1]</t>
+          <t xml:space="preserve">ovr_elite.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5119,14 +5119,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">戻ってきたのに…ビビってんのかよ、あたし</t>
+          <t xml:space="preserve">ここまで来たら、もう誰にも止められねえ</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.normal.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.normal.delinquent[1]</t>
+          <t xml:space="preserve">ovr_growth.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5151,14 +5151,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治ったっつーのに…気力が戻んねー</t>
+          <t xml:space="preserve">おっ、ちょっとは強くなったじゃん</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.normal.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5168,29 +5168,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.normal.delinquent[1]</t>
+          <t xml:space="preserve">ovr_legend.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合はヤバかった。体が勝手に動いてた。あいつとじゃなきゃ無理だった</t>
+          <t xml:space="preserve">はは…マジかよ、こんなとこまで来ちまった</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.normal.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.delinquent[1]</t>
+          <t xml:space="preserve">pop_growth.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルト欲しいやつ、いくらでもかかってこい。全員叩き返す</t>
+          <t xml:space="preserve">おっ、知名度上がってんじゃん</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.normal.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5232,29 +5232,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.normal.delinquent[1]</t>
+          <t xml:space="preserve">pop_star.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まさかこんな名誉あるもんもらえる日が来るとはな…。全部、リングがくれたもんだ</t>
+          <t xml:space="preserve">すっげえ声援だな…やべえ、ちょっと鳥肌立った</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.delinquent[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5264,29 +5264,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっ、マジで？ やっべ、嬉しい</t>
+          <t xml:space="preserve">何のために闘ってんだよ…もうわかんねー</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.normal.delinquent[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5296,29 +5296,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間ずっと全力だった。手抜いた日なんか一日もねえよ</t>
+          <t xml:space="preserve">まだやれる…やってやるよ</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.normal.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5328,29 +5328,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直ビビってる。こんなちゃんとした賞もらったの初めてだ…来年も取る</t>
+          <t xml:space="preserve">やっと…やっと戻ってこれたぜ</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5360,29 +5360,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">defeat.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おい、ここがドームってやつか。デカいな</t>
+          <t xml:space="preserve">あの負けから…何かおかしいんだよ</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5392,29 +5392,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">injury_moderate_recovery.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まぁ、悪くねえ気分だ</t>
+          <t xml:space="preserve">体は治ったはずだろ…なんで動けねーんだ</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.delinquent[3]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5424,29 +5424,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[3]</t>
+          <t xml:space="preserve">injury_severe_recovery.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふん、やってやるよ。ドームだろうが同じだろ</t>
+          <t xml:space="preserve">戻ってきたのに…ビビってんのかよ、あたし</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5456,29 +5456,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">penalty_end.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…マジかよ、満員だって?</t>
+          <t xml:space="preserve">怪我は治ったっつーのに…気力が戻んねー</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">bestMatch.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5503,14 +5503,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっそ、これがドーム満員ってやつか…</t>
+          <t xml:space="preserve">あの試合はヤバかった。体が勝手に動いてた。あいつとじゃなきゃ無理だった</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.delinquent[3]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[3]</t>
+          <t xml:space="preserve">champion.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5535,14 +5535,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くねえな。…全然悪くねえ</t>
+          <t xml:space="preserve">このベルト欲しいやつ、いくらでもかかってこい。全員叩き返す</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5552,29 +5552,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal.delinquent[1]</t>
+          <t xml:space="preserve">hallOfFame.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか最近、体の動きキレてね？</t>
+          <t xml:space="preserve">まさかこんな名誉あるもんもらえる日が来るとはな…。全部、リングがくれたもんだ</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.delinquent[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5584,29 +5584,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal.delinquent[2]</t>
+          <t xml:space="preserve">mediaAward.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと感覚掴めてきたっぽい</t>
+          <t xml:space="preserve">えっ、マジで？ やっべ、嬉しい</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.normal.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5616,29 +5616,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.normal.delinquent[1]</t>
+          <t xml:space="preserve">mvp.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつと一緒だと楽しいんだよな</t>
+          <t xml:space="preserve">一年間ずっと全力だった。手抜いた日なんか一日もねえよ</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.normal.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5648,29 +5648,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.normal.delinquent[1]</t>
+          <t xml:space="preserve">rookie.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっとダルいだけだって。すぐ戻る</t>
+          <t xml:space="preserve">正直ビビってる。こんなちゃんとした賞もらったの初めてだ…来年も取る</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.normal.delinquent[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5680,29 +5680,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれるやつがいるってのは…悪くねえな</t>
+          <t xml:space="preserve">おい、ここがドームってやつか。デカいな</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.normal.delinquent[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5712,29 +5712,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もういいわ。勝手にする</t>
+          <t xml:space="preserve">…まぁ、悪くねえ気分だ</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.normal.delinquent[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.delinquent[3]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5744,29 +5744,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[3]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…別に。何でもねーよ</t>
+          <t xml:space="preserve">ふん、やってやるよ。ドームだろうが同じだろ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.normal.delinquent[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5776,29 +5776,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チッ</t>
+          <t xml:space="preserve">…マジかよ、満員だって?</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.normal.delinquent[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5808,29 +5808,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は？ ケチくさ。いらねーよ、こんなん</t>
+          <t xml:space="preserve">くっそ、これがドーム満員ってやつか…</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.normal.delinquent[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.delinquent[3]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5840,29 +5840,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[3]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、マジ？ ありがとな！</t>
+          <t xml:space="preserve">…悪くねえな。…全然悪くねえ</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.normal.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5872,29 +5872,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.normal.delinquent[1]</t>
+          <t xml:space="preserve">N1.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿！ ガンガンやるぞ！</t>
+          <t xml:space="preserve">なんか最近、体の動きキレてね？</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.normal.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5904,29 +5904,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.normal.delinquent[1]</t>
+          <t xml:space="preserve">N1.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…アンタに言われると、やんなきゃって思うんだよ</t>
+          <t xml:space="preserve">やっと感覚掴めてきたっぽい</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.normal.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5936,29 +5936,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.normal.delinquent[1]</t>
+          <t xml:space="preserve">N2.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…サンキュ。もうちょいやってみるわ</t>
+          <t xml:space="preserve">あいつと一緒だと楽しいんだよな</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.normal.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5968,29 +5968,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.normal.delinquent[1]</t>
+          <t xml:space="preserve">N3.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ？ やってやるよ！</t>
+          <t xml:space="preserve">ちょっとダルいだけだって。すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.normal.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6000,29 +6000,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.normal.delinquent[1]</t>
+          <t xml:space="preserve">N4.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえーい！カンパーイ！</t>
+          <t xml:space="preserve">応援してくれるやつがいるってのは…悪くねえな</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.normal.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6032,29 +6032,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.normal.delinquent[1]</t>
+          <t xml:space="preserve">N5_low.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">サンキュ！ちょっと休んでくるわ</t>
+          <t xml:space="preserve">…もういいわ。勝手にする</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.normal.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6064,29 +6064,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.normal.delinquent[1]</t>
+          <t xml:space="preserve">N5_warning.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっしゃ、ガンガンやるぞ！</t>
+          <t xml:space="preserve">…別に。何でもねーよ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.delinquent[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6096,29 +6096,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.normal.delinquent[1]</t>
+          <t xml:space="preserve">G1.voice.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ出れんの？ やるやる！</t>
+          <t xml:space="preserve">…チッ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.normal.delinquent[1]</t>
+          <t xml:space="preserve">bonus_insult.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6143,14 +6143,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所から話来てんだけど</t>
+          <t xml:space="preserve">は？ ケチくさ。いらねーよ、こんなん</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.normal.delinquent[1]</t>
+          <t xml:space="preserve">bonus.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6175,14 +6175,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習？やる意味あんの？出してもらえねぇんじゃ同じだろ</t>
+          <t xml:space="preserve">お、マジ？ ありがとな！</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.normal.delinquent[1]</t>
+          <t xml:space="preserve">camp.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6207,14 +6207,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「マジふざけんな」とロッカーを蹴る音が聞こえてきた）</t>
+          <t xml:space="preserve">合宿！ ガンガンやるぞ！</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.normal.delinquent[1]</t>
+          <t xml:space="preserve">encourage_high_trust.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6239,14 +6239,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「もう我慢の限界」と不穏な投稿）</t>
+          <t xml:space="preserve">…アンタに言われると、やんなきゃって思うんだよ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.normal.delinquent[1]</t>
+          <t xml:space="preserve">encourage.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6271,14 +6271,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タイトルマッチ、組んでくれよ</t>
+          <t xml:space="preserve">…サンキュ。もうちょいやってみるわ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.normal.delinquent[1]</t>
+          <t xml:space="preserve">media.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6303,14 +6303,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつとの試合、組んでくれよ</t>
+          <t xml:space="preserve">テレビ？ やってやるよ！</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.normal.delinquent[1]</t>
+          <t xml:space="preserve">party.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6335,14 +6335,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと休ませてくれ…</t>
+          <t xml:space="preserve">いえーい！カンパーイ！</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6352,12 +6352,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.normal.delinquent[1]</t>
+          <t xml:space="preserve">refresh_leave.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6367,14 +6367,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不満だっつってんの。ちゃんと話し合おうぜ</t>
+          <t xml:space="preserve">サンキュ！ちょっと休んでくるわ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.normal.delinquent[1]</t>
+          <t xml:space="preserve">special_treatment.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6399,14 +6399,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓させてくれ。もっと強くなりてえ</t>
+          <t xml:space="preserve">サンキュ。早く治してリング戻るわ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.normal.delinquent[1]</t>
+          <t xml:space="preserve">trainer.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6431,14 +6431,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の面倒、見させてくれよ</t>
+          <t xml:space="preserve">おっしゃ、ガンガンやるぞ！</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.normal.delinquent[1]</t>
+          <t xml:space="preserve">E1.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6463,14 +6463,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いてて…やっちまった。すぐ戻るから</t>
+          <t xml:space="preserve">テレビ出れんの？ やるやる！</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6480,12 +6480,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.normal.delinquent[1]</t>
+          <t xml:space="preserve">E4.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6495,14 +6495,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつとはもう無理だ。何とかしてくれ</t>
+          <t xml:space="preserve">新しいスカウトの話、来てるみたいっすよ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.normal.delinquent[1]</t>
+          <t xml:space="preserve">E6.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6527,14 +6527,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">向こうが悪いんだろ。なんで私だけ？</t>
+          <t xml:space="preserve">他所から話来てんだけど</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.normal.delinquent[1]</t>
+          <t xml:space="preserve">S_boycott.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6559,14 +6559,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ブランドとコラボ…？ なんか柄じゃないな。でもやる</t>
+          <t xml:space="preserve">練習？やる意味あんの？出してもらえねぇんじゃ同じだろ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.normal.delinquent[1]</t>
+          <t xml:space="preserve">S_grumble.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6591,14 +6591,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM！？ なんか恥ずかしいけど、やってやるよ</t>
+          <t xml:space="preserve">（「マジふざけんな」とロッカーを蹴る音が聞こえてきた）</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6608,12 +6608,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.normal.delinquent[1]</t>
+          <t xml:space="preserve">S_sns.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6623,14 +6623,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンイベ！ 直接会えるのいいな</t>
+          <t xml:space="preserve">（SNSに「もう我慢の限界」と不穏な投稿）</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.normal.delinquent[1]</t>
+          <t xml:space="preserve">S1.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6655,14 +6655,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファッションショー…？ 歩くだけ？ まぁいいけど</t>
+          <t xml:space="preserve">タイトルマッチ、組んでくれよ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.normal.delinquent[1]</t>
+          <t xml:space="preserve">S2.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6687,14 +6687,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビア…？ まぁ、やってやるか</t>
+          <t xml:space="preserve">あいつとの試合、組んでくれよ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.normal.delinquent[1]</t>
+          <t xml:space="preserve">S3.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6719,14 +6719,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティ？ 面白いことしてやるよ</t>
+          <t xml:space="preserve">ちょっと休ませてくれ…</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.normal.delinquent[1]</t>
+          <t xml:space="preserve">S4_direct.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6751,14 +6751,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">取材？ やってやるよ！</t>
+          <t xml:space="preserve">不満だっつってんの。ちゃんと話し合おうぜ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6768,29 +6768,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">S4_silent.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれるなら、全力で暴れるぜ</t>
+          <t xml:space="preserve">…（沈黙）…いや、なんでもねえよ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6800,29 +6800,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">S5.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
+          <t xml:space="preserve">特訓させてくれ。もっと強くなりてえ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6832,29 +6832,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">S6.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、期待しててくれよ</t>
+          <t xml:space="preserve">後輩の面倒、見させてくれよ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6864,29 +6864,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">B1.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
+          <t xml:space="preserve">いてて…やっちまった。すぐ戻るから</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6896,29 +6896,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">B2_fighter1.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな！ガンガンやるぜ</t>
+          <t xml:space="preserve">あいつとはもう無理だ。何とかしてくれ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6928,29 +6928,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">B2_fighter2.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ…やっちまったか</t>
+          <t xml:space="preserve">向こうが悪いんだろ。なんで私だけ？</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6960,29 +6960,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">B4_brand.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなんで休むの、カッコ悪いな</t>
+          <t xml:space="preserve">ブランドとコラボ…？ なんか柄じゃないな。でもやる</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6992,29 +6992,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.normal.delinquent[1]</t>
+          <t xml:space="preserve">B4_cm.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれるなら、全力で暴れるぜ</t>
+          <t xml:space="preserve">CM！？ なんか恥ずかしいけど、やってやるよ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7024,29 +7024,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.delinquent[1]</t>
+          <t xml:space="preserve">B4_fan.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
+          <t xml:space="preserve">ファンイベ！ 直接会えるのいいな</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.delinquent[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7056,29 +7056,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.delinquent[2]</t>
+          <t xml:space="preserve">B4_fashion.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、期待しててくれよ</t>
+          <t xml:space="preserve">ファッションショー…？ 歩くだけ？ まぁいいけど</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7088,29 +7088,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.normal.delinquent[1]</t>
+          <t xml:space="preserve">B4_gravure.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
+          <t xml:space="preserve">グラビア…？ まぁ、やってやるか</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7120,29 +7120,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.normal.delinquent[1]</t>
+          <t xml:space="preserve">B4_variety.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな！ガンガンやるぜ</t>
+          <t xml:space="preserve">バラエティ？ 面白いことしてやるよ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7152,29 +7152,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.delinquent[1]</t>
+          <t xml:space="preserve">B4.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ…やっちまったか</t>
+          <t xml:space="preserve">取材？ やってやるよ！</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7184,12 +7184,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.delinquent[2]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7199,14 +7199,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなんで休むの、カッコ悪いな</t>
+          <t xml:space="preserve">選んでくれるなら、全力で暴れるぜ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7231,14 +7231,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そうか…まぁ、縁がなかったってことだろ</t>
+          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.delinquent[2]</t>
+          <t xml:space="preserve">normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7263,14 +7263,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">世話になったな。どっかで見てろよ</t>
+          <t xml:space="preserve">まぁ、期待しててくれよ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7280,12 +7280,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7295,14 +7295,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな。手は抜かねーから</t>
+          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7327,14 +7327,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…次は絶対勝つ…！</t>
+          <t xml:space="preserve">よろしくな！ガンガンやるぜ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7359,14 +7359,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛だ！まだまだ渡さねーぞ！</t>
+          <t xml:space="preserve">ちっ…やっちまったか</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7376,12 +7376,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7391,14 +7391,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそ…ベルト取られた…でも終わりじゃねえ</t>
+          <t xml:space="preserve">こんなんで休むの、カッコ悪いな</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.normal.delinquent[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7423,14 +7423,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったぜ！チャンピオンだ！最高！</t>
+          <t xml:space="preserve">片付いた話を蒸し返すな。……いい加減、疲れるんだよ</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7440,12 +7440,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7455,14 +7455,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そうか…まぁ、縁がなかったってことだろ</t>
+          <t xml:space="preserve">終わった扱いされんのが、一番腹立つんだよ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">draftInterest.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7487,14 +7487,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">世話になったな。どっかで見てろよ</t>
+          <t xml:space="preserve">選んでくれるなら、全力で暴れるぜ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">draftJoin.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7519,14 +7519,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな。手は抜かねーから</t>
+          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">draftJoin.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7551,14 +7551,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…次は絶対勝つ…！</t>
+          <t xml:space="preserve">まぁ、期待しててくれよ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">faGreeting.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7583,14 +7583,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛だ！まだまだ渡さねーぞ！</t>
+          <t xml:space="preserve">拾われた借りは、リングで返す。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">faSigning.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7615,14 +7615,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそ…ベルト取られた…でも終わりじゃねえ</t>
+          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7632,12 +7632,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">faWelcome.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7647,14 +7647,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったぜ！チャンピオンだ！最高！</t>
+          <t xml:space="preserve">よろしくな！ガンガンやるぜ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7664,29 +7664,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">injury.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">顔見るとイラつくんだよ</t>
+          <t xml:space="preserve">ちっ…やっちまったか</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7696,29 +7696,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">injury.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近よそよそしくねぇか…</t>
+          <t xml:space="preserve">こんなんで休むの、カッコ悪いな</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7728,29 +7728,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">release.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると肩の力が抜けるっつーか</t>
+          <t xml:space="preserve">そうか…まぁ、縁がなかったってことだろ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7760,29 +7760,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.delinquent[2]</t>
+          <t xml:space="preserve">release.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ…悪くないやつだよ</t>
+          <t xml:space="preserve">世話になったな。どっかで見てろよ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7792,29 +7792,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">rentalGreeting.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ダチだ。何があっても守ってやる</t>
+          <t xml:space="preserve">よろしくな。手は抜かねーから</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7824,29 +7824,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">scoutGreeting.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう興味ねーよ</t>
+          <t xml:space="preserve">よく見つけたな。損はさせねーよ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7856,29 +7856,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目障りなんだよ…ぶっ潰してやる</t>
+          <t xml:space="preserve">くそっ…次は絶対勝つ…！</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7888,29 +7888,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">titleDefense.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対ぶっ倒す。覚悟しろ</t>
+          <t xml:space="preserve">防衛だ！まだまだ渡さねーぞ！</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7920,29 +7920,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">titleLoss.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この勝負が全てだ。他はどうでもいい</t>
+          <t xml:space="preserve">くそ…ベルト取られた…でも終わりじゃねえ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7952,29 +7952,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.delinquent[1]</t>
+          <t xml:space="preserve">titleWin.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここはあたしの場所だ。誰にも渡さねぇ</t>
+          <t xml:space="preserve">やったぜ！チャンピオンだ！最高！</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7984,29 +7984,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなとこ、もういられるか。出て行ってやる</t>
+          <t xml:space="preserve">そうか…まぁ、縁がなかったってことだろ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8016,29 +8016,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここ、ちゃんとしてんのかよ…不安になるぜ</t>
+          <t xml:space="preserve">世話になったな。どっかで見てろよ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8048,29 +8048,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたけど…あいつ、やるじゃねぇか</t>
+          <t xml:space="preserve">よろしくな。手は抜かねーから</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8080,29 +8080,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合で最高の結果だ。文句ねぇだろ</t>
+          <t xml:space="preserve">くそっ…次は絶対勝つ…！</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8112,29 +8112,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ…次は絶対ぶっ倒す</t>
+          <t xml:space="preserve">防衛だ！まだまだ渡さねーぞ！</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8144,29 +8144,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったぜ。当然だろ</t>
+          <t xml:space="preserve">くそ…ベルト取られた…でも終わりじゃねえ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8176,29 +8176,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一本いくぞ、おら！</t>
+          <t xml:space="preserve">やったぜ！チャンピオンだ！最高！</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.normal.delinquent[1]</t>
+          <t xml:space="preserve">bond_39_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8223,14 +8223,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おい、最近の扱い何だよ…舐めてんのか</t>
+          <t xml:space="preserve">顔見るとイラつくんだよ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.normal.delinquent[1]</t>
+          <t xml:space="preserve">bond_59_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8255,14 +8255,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここも悪くねぇな。やる気出てきたぜ</t>
+          <t xml:space="preserve">最近よそよそしくねぇか…</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.normal.delinquent[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8287,14 +8287,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">つるむの、結構楽しいんだよな</t>
+          <t xml:space="preserve">一緒にいると肩の力が抜けるっつーか</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.normal.delinquent[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8319,14 +8319,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">顔が頭から離れねぇんだよ</t>
+          <t xml:space="preserve">まぁ…悪くないやつだよ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.normal.delinquent[1]</t>
+          <t xml:space="preserve">bond_80_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8351,14 +8351,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんで出してくれねぇんだよ…腕が鳴ってんのに</t>
+          <t xml:space="preserve">ダチだ。何があっても守ってやる</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.normal.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8383,14 +8383,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそ…体がついてこねぇ</t>
+          <t xml:space="preserve">…もう興味ねーよ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.normal.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8415,14 +8415,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそが…何連敗してんだよあたしは…</t>
+          <t xml:space="preserve">目障りなんだよ…ぶっ潰してやる</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.normal.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8447,14 +8447,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちまくってるぜ。誰か止めてみろよ</t>
+          <t xml:space="preserve">絶対ぶっ倒す。覚悟しろ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.normal.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8479,14 +8479,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそ、いつまで寝てりゃいいんだよ…</t>
+          <t xml:space="preserve">この勝負が全てだ。他はどうでもいい</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8496,12 +8496,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.normal.delinquent[1]</t>
+          <t xml:space="preserve">trust_above_75.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8511,14 +8511,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー、いるな。それで?……別に</t>
+          <t xml:space="preserve">ここはあたしの場所だ。誰にも渡さねぇ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">trust_below_20.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8543,14 +8543,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チッ、終わっちまったか。まぁ上等だ</t>
+          <t xml:space="preserve">こんなとこ、もういられるか。出て行ってやる</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8560,29 +8560,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.delinquent[1]</t>
+          <t xml:space="preserve">trust_below_35.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体ガタガタだけどよ。最後だ、引けるわけねえだろ</t>
+          <t xml:space="preserve">ここ、ちゃんとしてんのかよ…不安になるぜ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8592,29 +8592,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.delinquent[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">傷だらけ上等。この一戦、あたしが全部背負ってやる</t>
+          <t xml:space="preserve">負けたけど…あいつ、やるじゃねぇか</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8624,29 +8624,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰だ? 何人来ようが、あたしがここで止めてやる</t>
+          <t xml:space="preserve">最高の試合で最高の結果だ。文句ねぇだろ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8656,29 +8656,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.delinquent[2]</t>
+          <t xml:space="preserve">GL-01.loss.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリング、通れると思ってんのか。かかってこいよ</t>
+          <t xml:space="preserve">ちっ…次は絶対ぶっ倒す</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8688,29 +8688,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-01.win.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人潰した。…はぁ…まだ立ってんだよ。次、さっさと出てこいや</t>
+          <t xml:space="preserve">勝ったぜ。当然だろ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8720,29 +8720,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.delinquent[2]</t>
+          <t xml:space="preserve">GL-02.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わってねえぞ。息? 上がってるけど関係ねえ。次、来い</t>
+          <t xml:space="preserve">もう一本いくぞ、おら！</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8752,29 +8752,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-03.down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人でもぎ取った勝ちだ。あたし一人の手柄じゃねえよ</t>
+          <t xml:space="preserve">おい、最近の扱い何だよ…舐めてんのか</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8784,29 +8784,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.delinquent[2]</t>
+          <t xml:space="preserve">GL-03.up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれたから、あたしはここにいる。それだけだろ</t>
+          <t xml:space="preserve">ここも悪くねぇな。やる気出てきたぜ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8816,29 +8816,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-04.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPったって、団体が負けてちゃ意味ねえよ。次は全員で勝つ</t>
+          <t xml:space="preserve">つるむの、結構楽しいんだよな</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8848,29 +8848,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.delinquent[2]</t>
+          <t xml:space="preserve">GL-05.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞はもらっとく。けど、次は優勝旗も一緒にだ</t>
+          <t xml:space="preserve">顔が頭から離れねぇんだよ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8880,29 +8880,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-06.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ようが関係ねえ。全員倒して、最後に立ってんのがあたしだ</t>
+          <t xml:space="preserve">なんで出してくれねぇんだよ…腕が鳴ってんのに</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8912,29 +8912,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.delinquent[2]</t>
+          <t xml:space="preserve">GL-07.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足ガクガクだけどよ、膝はつかなかった。それが全部だろ</t>
+          <t xml:space="preserve">くそ…体がついてこねぇ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8944,29 +8944,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-08.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テッペン獲ったぜ！ でもまだ上がある</t>
+          <t xml:space="preserve">くそが…何連敗してんだよあたしは…</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8976,29 +8976,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.delinquent[2]</t>
+          <t xml:space="preserve">GL-09.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝…悪くねえな。もっと強くなってやる</t>
+          <t xml:space="preserve">勝ちまくってるぜ。誰か止めてみろよ</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9008,29 +9008,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-10.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…次は絶対負けねえ</t>
+          <t xml:space="preserve">くそ、いつまで寝てりゃいいんだよ…</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9040,29 +9040,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.delinquent[2]</t>
+          <t xml:space="preserve">GL-11.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなとこで終わってたまるか…</t>
+          <t xml:space="preserve">あー、いるな。それで?……別に</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9072,29 +9072,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.delinquent[1]</t>
+          <t xml:space="preserve">normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっし、一丁上がりだ。次もブチかます</t>
+          <t xml:space="preserve">チッ、終わっちまったか。まぁ上等だ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9104,12 +9104,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.delinquent[2]</t>
+          <t xml:space="preserve">preFinal.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9119,14 +9119,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ止まんねえぞ</t>
+          <t xml:space="preserve">身体ガタガタだけどよ。最後だ、引けるわけねえだろ</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.delinquent[1]</t>
+          <t xml:space="preserve">preFinal.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9151,14 +9151,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあまあやれたな。次はもっと暴れてやるぜ</t>
+          <t xml:space="preserve">傷だらけ上等。この一戦、あたしが全部背負ってやる</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9168,12 +9168,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.delinquent[2]</t>
+          <t xml:space="preserve">preMatch.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9183,14 +9183,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悪くねえ結果だ</t>
+          <t xml:space="preserve">相手は誰だ? 何人来ようが、あたしがここで止めてやる</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.delinquent[1]</t>
+          <t xml:space="preserve">preMatch.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9215,14 +9215,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝だぜ。最後もぶっ潰してやる</t>
+          <t xml:space="preserve">このリング、通れると思ってんのか。かかってこいよ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.delinquent[2]</t>
+          <t xml:space="preserve">survivor.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9247,14 +9247,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たんだ。もう引けねえ</t>
+          <t xml:space="preserve">一人潰した。…はぁ…まだ立ってんだよ。次、さっさと出てこいや</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.delinquent[1]</t>
+          <t xml:space="preserve">survivor.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9279,14 +9279,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっ潰す。それだけだ</t>
+          <t xml:space="preserve">まだ終わってねえぞ。息? 上がってるけど関係ねえ。次、来い</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9296,12 +9296,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.delinquent[2]</t>
+          <t xml:space="preserve">champion.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9311,14 +9311,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手とか関係ねえ。全力で行くだけだ</t>
+          <t xml:space="preserve">三人でもぎ取った勝ちだ。あたし一人の手柄じゃねえよ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.delinquent[1]</t>
+          <t xml:space="preserve">champion.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9343,14 +9343,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おう、出てやるよ。覚悟しとけ</t>
+          <t xml:space="preserve">仲間が繋いでくれたから、あたしはここにいる。それだけだろ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.delinquent[2]</t>
+          <t xml:space="preserve">defiant.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9375,14 +9375,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員まとめてかかって来いってんだ</t>
+          <t xml:space="preserve">MVPったって、団体が負けてちゃ意味ねえよ。次は全員で勝つ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">defiant.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9407,14 +9407,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けねーぞ。かかってこい</t>
+          <t xml:space="preserve">この賞はもらっとく。けど、次は優勝旗も一緒にだ</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">gauntlet.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9439,14 +9439,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうだ……！ これがウチの団体の力だ……！</t>
+          <t xml:space="preserve">何人来ようが関係ねえ。全員倒して、最後に立ってんのがあたしだ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">gauntlet.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9471,14 +9471,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺん獲ったぞ……！ 見てたか……！</t>
+          <t xml:space="preserve">足ガクガクだけどよ、膝はつかなかった。それが全部だろ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9488,12 +9488,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">champion.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9503,14 +9503,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おい、聞いたぜ？ 弱小団体がイキってるってな</t>
+          <t xml:space="preserve">テッペン獲ったぜ！ でもまだ上がある</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">champion.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9535,14 +9535,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ボコボコにしてやっから、覚悟しとけ</t>
+          <t xml:space="preserve">優勝…悪くねえな。もっと強くなってやる</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">postLose.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9567,14 +9567,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、逃げやがった。ビビりが</t>
+          <t xml:space="preserve">くそっ…次は絶対負けねえ</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">postLose.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9599,14 +9599,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チキンかよ。次はねえぞ</t>
+          <t xml:space="preserve">こんなとこで終わってたまるか…</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9616,12 +9616,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.delinquent[1]</t>
+          <t xml:space="preserve">postMatchWin.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9631,14 +9631,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…やられた…。次は絶対ぶっ潰す</t>
+          <t xml:space="preserve">おっし、一丁上がりだ。次もブチかます</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9648,12 +9648,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.delinquent[2]</t>
+          <t xml:space="preserve">postMatchWin.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9663,14 +9663,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この借り…倍にして返してやるからな</t>
+          <t xml:space="preserve">まだまだ止まんねえぞ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.delinquent[1]</t>
+          <t xml:space="preserve">postWin.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9695,14 +9695,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうだ、これがウチの実力だ。舐めんなよ</t>
+          <t xml:space="preserve">まあまあやれたな。次はもっと暴れてやるぜ</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9712,12 +9712,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.delinquent[2]</t>
+          <t xml:space="preserve">postWin.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9727,14 +9727,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったぜ。ま、当然だけどな</t>
+          <t xml:space="preserve">悪くねえ結果だ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">preFinal.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9759,14 +9759,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">舐めんなよ。うちの団体はこんなもんじゃねえ</t>
+          <t xml:space="preserve">決勝だぜ。最後もぶっ潰してやる</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9776,12 +9776,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">preFinal.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9791,14 +9791,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったぜ。文句あるか？</t>
+          <t xml:space="preserve">ここまで来たんだ。もう引けねえ</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.delinquent[3]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[3]</t>
+          <t xml:space="preserve">preMatch.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9823,44 +9823,652 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽勝だぜ。次もかかってこいよ</t>
+          <t xml:space="preserve">ぶっ潰す。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">相手とか関係ねえ。全力で行くだけだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">おう、出てやるよ。覚悟しとけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全員まとめてかかって来いってんだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日は負けねーぞ。かかってこい</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">どうだ……！ これがウチの団体の力だ……！</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">てっぺん獲ったぞ……！ 見てたか……！</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">おい、聞いたぜ？ 弱小団体がイキってるってな</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ボコボコにしてやっから、覚悟しとけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">はっ、逃げやがった。ビビりが</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">チキンかよ。次はねえぞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">くそっ…やられた…。次は絶対ぶっ潰す</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この借り…倍にして返してやるからな</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">どうだ、これがウチの実力だ。舐めんなよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ったぜ。ま、当然だけどな</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">舐めんなよ。うちの団体はこんなもんじゃねえ</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ったぜ。文句あるか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="40" customHeight="1">
+      <c r="A313" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.normal.delinquent[3]</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.delinquent[3]</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">楽勝だぜ。次もかかってこいよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="40" customHeight="1">
+      <c r="A314" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.normal.delinquent[1]</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr" s="2">
+      <c r="B314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr" s="12">
+      <c r="D314" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.normal.delinquent[1]</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr" s="2">
+      <c r="E314" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr" s="3">
+      <c r="F314" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">やってやったぜ！最高だ！</t>
         </is>
       </c>
     </row>
+    <row r="315" ht="40" customHeight="1">
+      <c r="A315" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">拾われた借りは、リングで返す。それだけだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="40" customHeight="1">
+      <c r="A316" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よく見つけたな。損はさせねーよ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H297"/>
+  <autoFilter ref="A1:H316"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/ヤンキー×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/ヤンキー×ノーマル.xlsx
@@ -386,7 +386,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.delinquent[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -401,7 +401,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.delinquent[1]</t>
+          <t xml:space="preserve">atk.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -418,7 +418,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.delinquent[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -433,7 +433,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.delinquent[2]</t>
+          <t xml:space="preserve">atk.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -450,7 +450,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.delinquent[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -465,7 +465,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.delinquent[3]</t>
+          <t xml:space="preserve">atk.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -482,7 +482,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.normal.delinquent[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.delinquent.normal[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -497,7 +497,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.normal.delinquent[4]</t>
+          <t xml:space="preserve">atk.delinquent.normal[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -514,7 +514,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.delinquent[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -529,7 +529,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.delinquent[1]</t>
+          <t xml:space="preserve">bigmove.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -546,7 +546,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.delinquent[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -561,7 +561,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.delinquent[2]</t>
+          <t xml:space="preserve">bigmove.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -578,7 +578,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.normal.delinquent[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -593,7 +593,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.normal.delinquent[3]</t>
+          <t xml:space="preserve">bigmove.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -610,7 +610,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.normal.delinquent[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -625,7 +625,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.normal.delinquent[1]</t>
+          <t xml:space="preserve">climax.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -642,7 +642,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.normal.delinquent[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -657,7 +657,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.normal.delinquent[2]</t>
+          <t xml:space="preserve">climax.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -674,7 +674,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -689,7 +689,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -706,7 +706,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -721,7 +721,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -738,7 +738,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.normal.delinquent[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -753,7 +753,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.normal[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -770,7 +770,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.normal.delinquent[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -785,7 +785,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.normal.delinquent[1]</t>
+          <t xml:space="preserve">badWinner.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -802,7 +802,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal.delinquent[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -817,7 +817,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.normal.delinquent[1]</t>
+          <t xml:space="preserve">goodWinner.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -834,7 +834,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.normal.delinquent[2]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -849,7 +849,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.normal.delinquent[2]</t>
+          <t xml:space="preserve">goodWinner.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -866,7 +866,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -881,7 +881,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -898,7 +898,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -913,7 +913,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -930,7 +930,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal.delinquent[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -945,7 +945,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.delinquent[1]</t>
+          <t xml:space="preserve">loser.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -962,7 +962,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal.delinquent[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -977,7 +977,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.delinquent[2]</t>
+          <t xml:space="preserve">loser.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -994,7 +994,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.normal.delinquent[3]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.delinquent[3]</t>
+          <t xml:space="preserve">loser.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -1026,7 +1026,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal.delinquent[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.delinquent[1]</t>
+          <t xml:space="preserve">winner.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1058,7 +1058,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.normal.delinquent[2]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.delinquent[2]</t>
+          <t xml:space="preserve">winner.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1090,7 +1090,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.normal.delinquent[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.normal.delinquent[1]</t>
+          <t xml:space="preserve">competition_won.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1122,7 +1122,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.normal.delinquent[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.normal.delinquent[2]</t>
+          <t xml:space="preserve">competition_won.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1154,7 +1154,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.normal.delinquent[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.normal.delinquent[1]</t>
+          <t xml:space="preserve">direct.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1186,7 +1186,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.normal.delinquent[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.normal.delinquent[2]</t>
+          <t xml:space="preserve">direct.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1218,7 +1218,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.normal.delinquent[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.normal.delinquent[1]</t>
+          <t xml:space="preserve">fa_signing.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1250,7 +1250,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.normal.delinquent[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.normal.delinquent[2]</t>
+          <t xml:space="preserve">fa_signing.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1282,7 +1282,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.delinquent.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.delinquent.normal.hit[1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent.hit[1]</t>
+          <t xml:space="preserve">delinquent.normal.hit[1]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1314,7 +1314,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.delinquent.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.delinquent.normal.hit[2]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent.hit[2]</t>
+          <t xml:space="preserve">delinquent.normal.hit[2]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1346,7 +1346,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.delinquent.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.delinquent.normal.win[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent.win[1]</t>
+          <t xml:space="preserve">delinquent.normal.win[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1378,7 +1378,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.delinquent.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.delinquent.normal.win[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent.win[2]</t>
+          <t xml:space="preserve">delinquent.normal.win[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1410,7 +1410,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1442,7 +1442,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1474,7 +1474,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.normal.delinquent[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.normal[3]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1506,7 +1506,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1538,7 +1538,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1570,7 +1570,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.normal.delinquent[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.normal[3]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1602,7 +1602,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1634,7 +1634,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1666,7 +1666,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.normal.delinquent[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.normal[3]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1698,7 +1698,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1730,7 +1730,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1762,7 +1762,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.normal.delinquent[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.normal[3]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1794,7 +1794,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1826,7 +1826,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1858,7 +1858,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1890,7 +1890,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1922,7 +1922,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.normal.delinquent[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.normal.delinquent[1]</t>
+          <t xml:space="preserve">ahead.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1954,7 +1954,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.normal.delinquent[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.normal.delinquent[1]</t>
+          <t xml:space="preserve">behind.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1986,7 +1986,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.normal.delinquent[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.delinquent[1]</t>
+          <t xml:space="preserve">loser.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -2018,7 +2018,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.normal.delinquent[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.delinquent[1]</t>
+          <t xml:space="preserve">winner.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2050,7 +2050,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.normal.delinquent[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.delinquent[1]</t>
+          <t xml:space="preserve">loser.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2082,7 +2082,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.normal.delinquent[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.delinquent[1]</t>
+          <t xml:space="preserve">winner.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2114,7 +2114,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.delinquent[1]</t>
+          <t xml:space="preserve">attacker.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2146,7 +2146,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.normal.delinquent[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.delinquent[2]</t>
+          <t xml:space="preserve">attacker.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2178,7 +2178,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.delinquent[1]</t>
+          <t xml:space="preserve">defender.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2210,7 +2210,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.normal.delinquent[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.delinquent[2]</t>
+          <t xml:space="preserve">defender.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2242,7 +2242,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.delinquent[1]</t>
+          <t xml:space="preserve">attacker.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2274,7 +2274,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.delinquent[1]</t>
+          <t xml:space="preserve">defender.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2306,7 +2306,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.delinquent[1]</t>
+          <t xml:space="preserve">attacker.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2338,7 +2338,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.normal.delinquent[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.normal.delinquent[2]</t>
+          <t xml:space="preserve">attacker.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2370,7 +2370,7 @@
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.delinquent[1]</t>
+          <t xml:space="preserve">defender.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2402,7 +2402,7 @@
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.normal.delinquent[2]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.normal.delinquent[2]</t>
+          <t xml:space="preserve">defender.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2434,7 +2434,7 @@
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.normal.delinquent[1]</t>
+          <t xml:space="preserve">fateAttacker.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2466,7 +2466,7 @@
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.normal.delinquent[1]</t>
+          <t xml:space="preserve">fateDefender.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2498,7 +2498,7 @@
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.delinquent[1]</t>
+          <t xml:space="preserve">loserLines.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2530,7 +2530,7 @@
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.delinquent[1]</t>
+          <t xml:space="preserve">winnerLines.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2562,7 +2562,7 @@
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.normal.delinquent[1]</t>
+          <t xml:space="preserve">fateLoser.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2594,7 +2594,7 @@
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.normal.delinquent[1]</t>
+          <t xml:space="preserve">fateWinner.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2626,7 +2626,7 @@
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.normal.delinquent[1]</t>
+          <t xml:space="preserve">loser.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2658,7 +2658,7 @@
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.normal.delinquent[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.normal.delinquent[1]</t>
+          <t xml:space="preserve">winner.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2690,7 +2690,7 @@
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.normal.delinquent[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.normal.delinquent[1]</t>
+          <t xml:space="preserve">loserLines.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2722,7 +2722,7 @@
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.normal.delinquent[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.normal.delinquent[1]</t>
+          <t xml:space="preserve">winnerLines.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
@@ -2754,7 +2754,7 @@
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.normal.delinquent[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.normal.delinquent[1]</t>
+          <t xml:space="preserve">awakening.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
@@ -3554,7 +3554,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.delinquent[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.normal.delinquent[1]</t>
+          <t xml:space="preserve">accepted.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3586,7 +3586,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal.delinquent[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.normal.delinquent[2]</t>
+          <t xml:space="preserve">accepted.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3618,7 +3618,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.delinquent[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.normal.delinquent[1]</t>
+          <t xml:space="preserve">defended.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3650,7 +3650,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal.delinquent[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.normal.delinquent[2]</t>
+          <t xml:space="preserve">defended.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3682,7 +3682,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.delinquent[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.normal.delinquent[1]</t>
+          <t xml:space="preserve">defense_failed.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3714,7 +3714,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal.delinquent[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.normal.delinquent[2]</t>
+          <t xml:space="preserve">defense_failed.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3746,7 +3746,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.normal.delinquent[1]</t>
+          <t xml:space="preserve">default.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3778,7 +3778,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.normal.delinquent[1]</t>
+          <t xml:space="preserve">former_champ.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3810,7 +3810,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.normal.delinquent[1]</t>
+          <t xml:space="preserve">heel.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3842,7 +3842,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.normal.delinquent[1]</t>
+          <t xml:space="preserve">high_trust.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3874,7 +3874,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.normal.delinquent[1]</t>
+          <t xml:space="preserve">accept_former_champ.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3906,7 +3906,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.normal.delinquent[1]</t>
+          <t xml:space="preserve">accept_heel.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3938,7 +3938,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.normal.delinquent[1]</t>
+          <t xml:space="preserve">accept_no_title.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3970,7 +3970,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.normal.delinquent[1]</t>
+          <t xml:space="preserve">accept_terminal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -4002,7 +4002,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.normal.delinquent[1]</t>
+          <t xml:space="preserve">accept_winless.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4034,7 +4034,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.normal.delinquent[1]</t>
+          <t xml:space="preserve">refuse_champ.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4066,7 +4066,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.normal.delinquent[1]</t>
+          <t xml:space="preserve">refuse_distrust.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4098,7 +4098,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.normal.delinquent[1]</t>
+          <t xml:space="preserve">refuse_fighting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4130,7 +4130,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.normal.delinquent[1]</t>
+          <t xml:space="preserve">refuse_heel.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4162,7 +4162,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.normal.delinquent[1]</t>
+          <t xml:space="preserve">A1_champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4194,7 +4194,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.normal.delinquent[1]</t>
+          <t xml:space="preserve">A2_uncrowned.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4226,7 +4226,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.normal.delinquent[1]</t>
+          <t xml:space="preserve">A3_heel.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4258,7 +4258,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.normal.delinquent[1]</t>
+          <t xml:space="preserve">A4_veteran.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4290,7 +4290,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.normal.delinquent[1]</t>
+          <t xml:space="preserve">B1_young.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4322,7 +4322,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.normal.delinquent[1]</t>
+          <t xml:space="preserve">B2_prime.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4354,7 +4354,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.normal.delinquent[1]</t>
+          <t xml:space="preserve">B3_older.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4386,7 +4386,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal.delinquent[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.normal.delinquent[1]</t>
+          <t xml:space="preserve">B4_champion_injury.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4418,7 +4418,7 @@
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4450,7 +4450,7 @@
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.normal.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.normal.delinquent[1]</t>
+          <t xml:space="preserve">raise_accept.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4482,7 +4482,7 @@
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.normal.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.normal.delinquent[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4514,7 +4514,7 @@
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.normal.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.normal.delinquent[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4546,7 +4546,7 @@
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.normal.delinquent[1]</t>
+          <t xml:space="preserve">raise_open.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4578,7 +4578,7 @@
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.normal.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.normal.delinquent[1]</t>
+          <t xml:space="preserve">raise_refuse.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4610,7 +4610,7 @@
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.normal.delinquent[1]</t>
+          <t xml:space="preserve">sudden_departure.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4642,7 +4642,7 @@
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal.delinquent[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.normal.delinquent[2]</t>
+          <t xml:space="preserve">sudden_departure.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4674,7 +4674,7 @@
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.normal.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.normal.delinquent[1]</t>
+          <t xml:space="preserve">transfer_listen.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4706,7 +4706,7 @@
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.normal.delinquent[1]</t>
+          <t xml:space="preserve">transfer_open.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4738,7 +4738,7 @@
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.normal.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.normal.delinquent[1]</t>
+          <t xml:space="preserve">transfer_release.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4770,7 +4770,7 @@
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.normal.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.normal.delinquent[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4802,7 +4802,7 @@
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.normal.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.normal.delinquent[1]</t>
+          <t xml:space="preserve">transfer_retain_success.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4834,7 +4834,7 @@
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.normal.delinquent[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.normal.delinquent[1]</t>
+          <t xml:space="preserve">blocked.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4867,7 +4867,7 @@
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.normal.delinquent[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.normal.delinquent[1]</t>
+          <t xml:space="preserve">fail.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4900,7 +4900,7 @@
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.normal.delinquent[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.normal.delinquent[1]</t>
+          <t xml:space="preserve">start.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4933,7 +4933,7 @@
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.normal.delinquent[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.normal.delinquent[1]</t>
+          <t xml:space="preserve">success.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4966,7 +4966,7 @@
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4998,7 +4998,7 @@
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5030,7 +5030,7 @@
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5062,7 +5062,7 @@
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.normal.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.normal.delinquent[1]</t>
+          <t xml:space="preserve">cap_reached.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5094,7 +5094,7 @@
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.normal.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.normal.delinquent[1]</t>
+          <t xml:space="preserve">ovr_elite.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5126,7 +5126,7 @@
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.normal.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.normal.delinquent[1]</t>
+          <t xml:space="preserve">ovr_growth.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5158,7 +5158,7 @@
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.normal.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.normal.delinquent[1]</t>
+          <t xml:space="preserve">ovr_legend.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5190,7 +5190,7 @@
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.normal.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.normal.delinquent[1]</t>
+          <t xml:space="preserve">pop_growth.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5222,7 +5222,7 @@
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.normal.delinquent[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.normal.delinquent[1]</t>
+          <t xml:space="preserve">pop_star.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5254,7 +5254,7 @@
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5286,7 +5286,7 @@
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5318,7 +5318,7 @@
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5350,7 +5350,7 @@
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.normal.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.normal.delinquent[1]</t>
+          <t xml:space="preserve">defeat.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5382,7 +5382,7 @@
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.normal.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.normal.delinquent[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5414,7 +5414,7 @@
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.normal.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.normal.delinquent[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5446,7 +5446,7 @@
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.normal.delinquent[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.normal.delinquent[1]</t>
+          <t xml:space="preserve">penalty_end.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5478,7 +5478,7 @@
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.normal.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.normal.delinquent[1]</t>
+          <t xml:space="preserve">bestMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5510,7 +5510,7 @@
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.normal.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.delinquent[1]</t>
+          <t xml:space="preserve">champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5542,7 +5542,7 @@
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.normal.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.normal.delinquent[1]</t>
+          <t xml:space="preserve">hallOfFame.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5574,7 +5574,7 @@
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.normal.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.normal.delinquent[1]</t>
+          <t xml:space="preserve">mediaAward.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5606,7 +5606,7 @@
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.normal.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.normal.delinquent[1]</t>
+          <t xml:space="preserve">mvp.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5638,7 +5638,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.normal.delinquent[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.normal.delinquent[1]</t>
+          <t xml:space="preserve">rookie.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5670,7 +5670,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5702,7 +5702,7 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5734,7 +5734,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.normal.delinquent[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.normal[3]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5766,7 +5766,7 @@
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5798,7 +5798,7 @@
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5830,7 +5830,7 @@
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.normal.delinquent[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.normal[3]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5862,7 +5862,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal.delinquent[1]</t>
+          <t xml:space="preserve">N1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5894,7 +5894,7 @@
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.normal.delinquent[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.normal.delinquent[2]</t>
+          <t xml:space="preserve">N1.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5926,7 +5926,7 @@
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.normal.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.normal.delinquent[1]</t>
+          <t xml:space="preserve">N2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5958,7 +5958,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.normal.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.normal.delinquent[1]</t>
+          <t xml:space="preserve">N3.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5990,7 +5990,7 @@
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.normal.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.normal.delinquent[1]</t>
+          <t xml:space="preserve">N4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6022,7 +6022,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.normal.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.normal.delinquent[1]</t>
+          <t xml:space="preserve">N5_low.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6054,7 +6054,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.normal.delinquent[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.normal.delinquent[1]</t>
+          <t xml:space="preserve">N5_warning.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6086,7 +6086,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.normal.delinquent[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.normal.delinquent[1]</t>
+          <t xml:space="preserve">G1.voice.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6118,7 +6118,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.normal.delinquent[1]</t>
+          <t xml:space="preserve">bonus_insult.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6150,7 +6150,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.normal.delinquent[1]</t>
+          <t xml:space="preserve">bonus.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6182,7 +6182,7 @@
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.normal.delinquent[1]</t>
+          <t xml:space="preserve">camp.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6214,7 +6214,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.normal.delinquent[1]</t>
+          <t xml:space="preserve">encourage_high_trust.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6246,7 +6246,7 @@
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.normal.delinquent[1]</t>
+          <t xml:space="preserve">encourage.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6278,7 +6278,7 @@
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.normal.delinquent[1]</t>
+          <t xml:space="preserve">media.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6310,7 +6310,7 @@
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.normal.delinquent[1]</t>
+          <t xml:space="preserve">party.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6342,7 +6342,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.normal.delinquent[1]</t>
+          <t xml:space="preserve">refresh_leave.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6374,7 +6374,7 @@
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.normal.delinquent[1]</t>
+          <t xml:space="preserve">special_treatment.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6406,7 +6406,7 @@
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.normal.delinquent[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.normal.delinquent[1]</t>
+          <t xml:space="preserve">trainer.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6438,7 +6438,7 @@
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.normal.delinquent[1]</t>
+          <t xml:space="preserve">E1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6470,7 +6470,7 @@
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.normal.delinquent[1]</t>
+          <t xml:space="preserve">E4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6502,7 +6502,7 @@
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.normal.delinquent[1]</t>
+          <t xml:space="preserve">E6.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6534,7 +6534,7 @@
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.normal.delinquent[1]</t>
+          <t xml:space="preserve">S_boycott.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6566,7 +6566,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.normal.delinquent[1]</t>
+          <t xml:space="preserve">S_grumble.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6598,7 +6598,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.normal.delinquent[1]</t>
+          <t xml:space="preserve">S_sns.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6630,7 +6630,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.normal.delinquent[1]</t>
+          <t xml:space="preserve">S1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6662,7 +6662,7 @@
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.normal.delinquent[1]</t>
+          <t xml:space="preserve">S2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6694,7 +6694,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.normal.delinquent[1]</t>
+          <t xml:space="preserve">S3.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6726,7 +6726,7 @@
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.normal.delinquent[1]</t>
+          <t xml:space="preserve">S4_direct.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6758,7 +6758,7 @@
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.normal.delinquent[1]</t>
+          <t xml:space="preserve">S4_silent.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6790,7 +6790,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.normal.delinquent[1]</t>
+          <t xml:space="preserve">S5.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6822,7 +6822,7 @@
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.normal.delinquent[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.normal.delinquent[1]</t>
+          <t xml:space="preserve">S6.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6854,7 +6854,7 @@
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.normal.delinquent[1]</t>
+          <t xml:space="preserve">B1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6886,7 +6886,7 @@
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.normal.delinquent[1]</t>
+          <t xml:space="preserve">B2_fighter1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6918,7 +6918,7 @@
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.normal.delinquent[1]</t>
+          <t xml:space="preserve">B2_fighter2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6950,7 +6950,7 @@
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.normal.delinquent[1]</t>
+          <t xml:space="preserve">B4_brand.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6982,7 +6982,7 @@
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.normal.delinquent[1]</t>
+          <t xml:space="preserve">B4_cm.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7014,7 +7014,7 @@
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.normal.delinquent[1]</t>
+          <t xml:space="preserve">B4_fan.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7046,7 +7046,7 @@
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.normal.delinquent[1]</t>
+          <t xml:space="preserve">B4_fashion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7078,7 +7078,7 @@
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.normal.delinquent[1]</t>
+          <t xml:space="preserve">B4_gravure.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7110,7 +7110,7 @@
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.normal.delinquent[1]</t>
+          <t xml:space="preserve">B4_variety.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7142,7 +7142,7 @@
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.normal.delinquent[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.normal.delinquent[1]</t>
+          <t xml:space="preserve">B4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7174,7 +7174,7 @@
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7206,7 +7206,7 @@
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7238,7 +7238,7 @@
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7270,7 +7270,7 @@
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7302,7 +7302,7 @@
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7334,7 +7334,7 @@
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7366,7 +7366,7 @@
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7398,7 +7398,7 @@
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.normal.delinquent[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7430,7 +7430,7 @@
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.normal.delinquent[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7462,7 +7462,7 @@
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.normal.delinquent[1]</t>
+          <t xml:space="preserve">draftInterest.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7494,7 +7494,7 @@
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.delinquent[1]</t>
+          <t xml:space="preserve">draftJoin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7526,7 +7526,7 @@
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal.delinquent[2]</t>
+          <t xml:space="preserve">draftJoin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7558,7 +7558,7 @@
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.normal.delinquent[1]</t>
+          <t xml:space="preserve">faGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7590,7 +7590,7 @@
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.normal.delinquent[1]</t>
+          <t xml:space="preserve">faSigning.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7622,7 +7622,7 @@
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.normal.delinquent[1]</t>
+          <t xml:space="preserve">faWelcome.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7654,7 +7654,7 @@
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.delinquent[1]</t>
+          <t xml:space="preserve">injury.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7686,7 +7686,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal.delinquent[2]</t>
+          <t xml:space="preserve">injury.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7718,7 +7718,7 @@
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.delinquent[1]</t>
+          <t xml:space="preserve">release.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7750,7 +7750,7 @@
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal.delinquent[2]</t>
+          <t xml:space="preserve">release.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7782,7 +7782,7 @@
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.normal.delinquent[1]</t>
+          <t xml:space="preserve">rentalGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7814,7 +7814,7 @@
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.normal.delinquent[1]</t>
+          <t xml:space="preserve">scoutGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7846,7 +7846,7 @@
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.normal.delinquent[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7878,7 +7878,7 @@
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.normal.delinquent[1]</t>
+          <t xml:space="preserve">titleDefense.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7910,7 +7910,7 @@
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.normal.delinquent[1]</t>
+          <t xml:space="preserve">titleLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7942,7 +7942,7 @@
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.normal.delinquent[1]</t>
+          <t xml:space="preserve">titleWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7974,7 +7974,7 @@
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -8006,7 +8006,7 @@
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8038,7 +8038,7 @@
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8070,7 +8070,7 @@
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8102,7 +8102,7 @@
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8134,7 +8134,7 @@
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8166,7 +8166,7 @@
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8582,7 +8582,7 @@
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8614,7 +8614,7 @@
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8646,7 +8646,7 @@
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-01.loss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8678,7 +8678,7 @@
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-01.win.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8710,7 +8710,7 @@
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-02.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8742,7 +8742,7 @@
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-03.down.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8774,7 +8774,7 @@
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-03.up.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8806,7 +8806,7 @@
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-04.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8838,7 +8838,7 @@
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-05.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8870,7 +8870,7 @@
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-06.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8902,7 +8902,7 @@
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-07.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8934,7 +8934,7 @@
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-08.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8966,7 +8966,7 @@
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-09.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8998,7 +8998,7 @@
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-10.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9030,7 +9030,7 @@
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.normal.delinquent[1]</t>
+          <t xml:space="preserve">GL-11.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9062,7 +9062,7 @@
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9094,7 +9094,7 @@
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.delinquent[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9126,7 +9126,7 @@
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.normal.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.delinquent[2]</t>
+          <t xml:space="preserve">preFinal.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9158,7 +9158,7 @@
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9173,7 +9173,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.delinquent[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9190,7 +9190,7 @@
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.normal.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.delinquent[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9222,7 +9222,7 @@
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.delinquent[1]</t>
+          <t xml:space="preserve">survivor.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9254,7 +9254,7 @@
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.normal.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.normal.delinquent[2]</t>
+          <t xml:space="preserve">survivor.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9286,7 +9286,7 @@
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.delinquent[1]</t>
+          <t xml:space="preserve">champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9318,7 +9318,7 @@
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.normal.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.delinquent[2]</t>
+          <t xml:space="preserve">champion.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9350,7 +9350,7 @@
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.delinquent[1]</t>
+          <t xml:space="preserve">defiant.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9382,7 +9382,7 @@
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.normal.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.normal.delinquent[2]</t>
+          <t xml:space="preserve">defiant.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9414,7 +9414,7 @@
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.delinquent[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.delinquent[1]</t>
+          <t xml:space="preserve">gauntlet.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9446,7 +9446,7 @@
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.normal.delinquent[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.normal.delinquent[2]</t>
+          <t xml:space="preserve">gauntlet.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9478,7 +9478,7 @@
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.delinquent[1]</t>
+          <t xml:space="preserve">champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9510,7 +9510,7 @@
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.normal.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.normal.delinquent[2]</t>
+          <t xml:space="preserve">champion.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9542,7 +9542,7 @@
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.delinquent[1]</t>
+          <t xml:space="preserve">postLose.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9574,7 +9574,7 @@
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.normal.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.normal.delinquent[2]</t>
+          <t xml:space="preserve">postLose.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9606,7 +9606,7 @@
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.delinquent[1]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9638,7 +9638,7 @@
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.normal.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.normal.delinquent[2]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9670,7 +9670,7 @@
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.delinquent[1]</t>
+          <t xml:space="preserve">postWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9702,7 +9702,7 @@
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.normal.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.normal.delinquent[2]</t>
+          <t xml:space="preserve">postWin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9734,7 +9734,7 @@
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.delinquent[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9766,7 +9766,7 @@
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.normal.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.normal.delinquent[2]</t>
+          <t xml:space="preserve">preFinal.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9798,7 +9798,7 @@
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.delinquent[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9830,7 +9830,7 @@
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.normal.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.normal.delinquent[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9862,7 +9862,7 @@
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.delinquent[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.delinquent[1]</t>
+          <t xml:space="preserve">summon.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9894,7 +9894,7 @@
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.normal.delinquent[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.normal.delinquent[2]</t>
+          <t xml:space="preserve">summon.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9926,7 +9926,7 @@
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9958,7 +9958,7 @@
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9990,7 +9990,7 @@
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10022,7 +10022,7 @@
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.delinquent[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10054,7 +10054,7 @@
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.normal.delinquent[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10086,7 +10086,7 @@
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.delinquent[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10101,7 +10101,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10118,7 +10118,7 @@
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.normal.delinquent[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10150,7 +10150,7 @@
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.delinquent[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.delinquent[1]</t>
+          <t xml:space="preserve">result_lose.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10182,7 +10182,7 @@
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.normal.delinquent[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.normal.delinquent[2]</t>
+          <t xml:space="preserve">result_lose.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10214,7 +10214,7 @@
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.delinquent[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.delinquent[1]</t>
+          <t xml:space="preserve">result_win.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10246,7 +10246,7 @@
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.normal.delinquent[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.normal.delinquent[2]</t>
+          <t xml:space="preserve">result_win.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10278,7 +10278,7 @@
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10310,7 +10310,7 @@
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.delinquent[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10342,7 +10342,7 @@
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.normal.delinquent[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[3]</t>
+          <t xml:space="preserve">delinquent.normal[3]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10374,7 +10374,7 @@
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.normal.delinquent[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.normal.delinquent[1]</t>
+          <t xml:space="preserve">fighter.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10406,7 +10406,7 @@
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10438,7 +10438,7 @@
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.normal.delinquent[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">

--- a/セリフ編集/キャラタイプ別/ヤンキー×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/ヤンキー×ノーマル.xlsx
@@ -328,7 +328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H316"/>
+  <dimension ref="A1:H318"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="F45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここからはあたしが行く！</t>
+          <t xml:space="preserve">ここからは私が行く！</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="F46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{partner}…悪い。あたしが決めてりゃな…</t>
+          <t xml:space="preserve">{partner}…悪い。私が決めてりゃな…</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったぜ{partner}！ あたしら、いいコンビだろ？</t>
+          <t xml:space="preserve">やったぜ{partner}！ 私ら、いいコンビだろ？</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうだ……！ これが俺の答えだ！</t>
+          <t xml:space="preserve">どうだ……！ これが私の答えだ！</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わんねーよ。あたしはまだ闘える</t>
+          <t xml:space="preserve">まだ終わんねーよ。私はまだ闘える</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしを引き抜くってか？
+          <t xml:space="preserve">私を引き抜くってか？
 …条件次第だな</t>
         </is>
       </c>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">戻ってきたのに…ビビってんのかよ、あたし</t>
+          <t xml:space="preserve">戻ってきたのに…ビビってんのかよ、私</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.delinquent.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.delinquent.normal[1]</t>
+          <t xml:space="preserve">autumnWarChampion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5503,14 +5503,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合はヤバかった。体が勝手に動いてた。あいつとじゃなきゃ無理だった</t>
+          <t xml:space="preserve">うちの団体をなめるなって、ちゃんと教えてやったよ。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.delinquent.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.normal[1]</t>
+          <t xml:space="preserve">bestMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5535,14 +5535,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルト欲しいやつ、いくらでもかかってこい。全員叩き返す</t>
+          <t xml:space="preserve">あの試合はヤバかった。体が勝手に動いてた。あいつとじゃなきゃ無理だった</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.delinquent.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.delinquent.normal[1]</t>
+          <t xml:space="preserve">champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5567,14 +5567,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まさかこんな名誉あるもんもらえる日が来るとはな…。全部、リングがくれたもんだ</t>
+          <t xml:space="preserve">このベルト欲しいやつ、いくらでもかかってこい。全員叩き返す</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.delinquent.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.delinquent.normal[1]</t>
+          <t xml:space="preserve">hallOfFame.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5599,14 +5599,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっ、マジで？ やっべ、嬉しい</t>
+          <t xml:space="preserve">まさかこんな名誉あるもんもらえる日が来るとはな…。全部、リングがくれたもんだ</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.delinquent.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.delinquent.normal[1]</t>
+          <t xml:space="preserve">mediaAward.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5631,14 +5631,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間ずっと全力だった。手抜いた日なんか一日もねえよ</t>
+          <t xml:space="preserve">えっ、マジで？ やっべ、嬉しい</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.delinquent.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.delinquent.normal[1]</t>
+          <t xml:space="preserve">mvp.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5663,14 +5663,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直ビビってる。こんなちゃんとした賞もらったの初めてだ…来年も取る</t>
+          <t xml:space="preserve">一年間ずっと全力だった。手抜いた日なんか一日もねえよ</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">rookie.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5695,14 +5695,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おい、ここがドームってやつか。デカいな</t>
+          <t xml:space="preserve">正直ビビってる。こんなちゃんとした賞もらったの初めてだ…来年も取る</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">springTagChampion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5727,14 +5727,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まぁ、悪くねえ気分だ</t>
+          <t xml:space="preserve">相棒と決めたことをやっただけだ。文句あるやつはかかってきな。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.normal[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[3]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5759,14 +5759,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふん、やってやるよ。ドームだろうが同じだろ</t>
+          <t xml:space="preserve">おい、ここがドームってやつか。デカいな</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5791,14 +5791,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…マジかよ、満員だって?</t>
+          <t xml:space="preserve">…まぁ、悪くねえ気分だ</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.normal[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">delinquent.normal[3]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5823,14 +5823,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっそ、これがドーム満員ってやつか…</t>
+          <t xml:space="preserve">ふん、やってやるよ。ドームだろうが同じだろ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.normal[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[3]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5855,14 +5855,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くねえな。…全然悪くねえ</t>
+          <t xml:space="preserve">…マジかよ、満員だって？</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5872,29 +5872,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか最近、体の動きキレてね？</t>
+          <t xml:space="preserve">くっそ、これがドーム満員ってやつか…</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.normal[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5904,29 +5904,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.delinquent.normal[2]</t>
+          <t xml:space="preserve">delinquent.normal[3]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと感覚掴めてきたっぽい</t>
+          <t xml:space="preserve">…悪くねえな。…全然悪くねえ</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.delinquent.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.delinquent.normal[1]</t>
+          <t xml:space="preserve">N1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5951,14 +5951,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつと一緒だと楽しいんだよな</t>
+          <t xml:space="preserve">なんか最近、体の動きキレてね？</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.delinquent.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.delinquent.normal[1]</t>
+          <t xml:space="preserve">N1.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5983,14 +5983,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっとダルいだけだって。すぐ戻る</t>
+          <t xml:space="preserve">やっと感覚掴めてきたっぽい</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.delinquent.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.delinquent.normal[1]</t>
+          <t xml:space="preserve">N2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6015,14 +6015,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれるやつがいるってのは…悪くねえな</t>
+          <t xml:space="preserve">あいつと一緒だと楽しいんだよな</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.delinquent.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.delinquent.normal[1]</t>
+          <t xml:space="preserve">N3.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6047,14 +6047,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もういいわ。勝手にする</t>
+          <t xml:space="preserve">ちょっとダルいだけだって。すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.delinquent.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.delinquent.normal[1]</t>
+          <t xml:space="preserve">N4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6079,14 +6079,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…別に。何でもねーよ</t>
+          <t xml:space="preserve">応援してくれるやつがいるってのは…悪くねえな</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.delinquent.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6096,12 +6096,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.delinquent.normal[1]</t>
+          <t xml:space="preserve">N5_low.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6111,14 +6111,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チッ</t>
+          <t xml:space="preserve">…もういいわ。勝手にする</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.delinquent.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6128,29 +6128,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.delinquent.normal[1]</t>
+          <t xml:space="preserve">N5_warning.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は？ ケチくさ。いらねーよ、こんなん</t>
+          <t xml:space="preserve">…別に。何でもねーよ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.delinquent.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6160,29 +6160,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.delinquent.normal[1]</t>
+          <t xml:space="preserve">G1.voice.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、マジ？ ありがとな！</t>
+          <t xml:space="preserve">…チッ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.delinquent.normal[1]</t>
+          <t xml:space="preserve">bonus_insult.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6207,14 +6207,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿！ ガンガンやるぞ！</t>
+          <t xml:space="preserve">は？ ケチくさ。いらねーよ、こんなん</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.delinquent.normal[1]</t>
+          <t xml:space="preserve">bonus.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6239,14 +6239,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…アンタに言われると、やんなきゃって思うんだよ</t>
+          <t xml:space="preserve">お、マジ？ ありがとな！</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.delinquent.normal[1]</t>
+          <t xml:space="preserve">camp.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6271,14 +6271,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…サンキュ。もうちょいやってみるわ</t>
+          <t xml:space="preserve">合宿！ ガンガンやるぞ！</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.delinquent.normal[1]</t>
+          <t xml:space="preserve">encourage_high_trust.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6303,14 +6303,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ？ やってやるよ！</t>
+          <t xml:space="preserve">…アンタに言われると、やんなきゃって思うんだよ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.delinquent.normal[1]</t>
+          <t xml:space="preserve">encourage.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6335,14 +6335,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえーい！カンパーイ！</t>
+          <t xml:space="preserve">…サンキュ。もうちょいやってみるわ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.delinquent.normal[1]</t>
+          <t xml:space="preserve">media.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6367,14 +6367,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">サンキュ！ちょっと休んでくるわ</t>
+          <t xml:space="preserve">テレビ？ やってやるよ！</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.delinquent.normal[1]</t>
+          <t xml:space="preserve">party.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6399,14 +6399,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">サンキュ。早く治してリング戻るわ</t>
+          <t xml:space="preserve">いえーい！カンパーイ！</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.delinquent.normal[1]</t>
+          <t xml:space="preserve">refresh_leave.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6431,14 +6431,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっしゃ、ガンガンやるぞ！</t>
+          <t xml:space="preserve">サンキュ！ちょっと休んでくるわ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.delinquent.normal[1]</t>
+          <t xml:space="preserve">special_treatment.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6463,14 +6463,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ出れんの？ やるやる！</t>
+          <t xml:space="preserve">サンキュ。早く治してリング戻るわ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6480,12 +6480,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.delinquent.normal[1]</t>
+          <t xml:space="preserve">trainer.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6495,14 +6495,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しいスカウトの話、来てるみたいっすよ</t>
+          <t xml:space="preserve">おっしゃ、ガンガンやるぞ！</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.delinquent.normal[1]</t>
+          <t xml:space="preserve">E1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6527,14 +6527,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所から話来てんだけど</t>
+          <t xml:space="preserve">テレビ出れんの？ やるやる！</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.delinquent.normal[1]</t>
+          <t xml:space="preserve">E4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6559,14 +6559,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習？やる意味あんの？出してもらえねぇんじゃ同じだろ</t>
+          <t xml:space="preserve">新しいスカウトの話、来てるみたいっすよ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.delinquent.normal[1]</t>
+          <t xml:space="preserve">E6.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6591,14 +6591,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「マジふざけんな」とロッカーを蹴る音が聞こえてきた）</t>
+          <t xml:space="preserve">他所から話来てんだけど</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.delinquent.normal[1]</t>
+          <t xml:space="preserve">S_boycott.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6623,14 +6623,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「もう我慢の限界」と不穏な投稿）</t>
+          <t xml:space="preserve">練習？やる意味あんの？出してもらえねぇんじゃ同じだろ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.delinquent.normal[1]</t>
+          <t xml:space="preserve">S_grumble.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6655,14 +6655,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タイトルマッチ、組んでくれよ</t>
+          <t xml:space="preserve">（「マジふざけんな」とロッカーを蹴る音が聞こえてきた）</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.delinquent.normal[1]</t>
+          <t xml:space="preserve">S_sns.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6687,14 +6687,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつとの試合、組んでくれよ</t>
+          <t xml:space="preserve">（SNSに「もう我慢の限界」と不穏な投稿）</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.delinquent.normal[1]</t>
+          <t xml:space="preserve">S1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6719,14 +6719,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと休ませてくれ…</t>
+          <t xml:space="preserve">タイトルマッチ、組んでくれよ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.delinquent.normal[1]</t>
+          <t xml:space="preserve">S2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6751,14 +6751,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不満だっつってんの。ちゃんと話し合おうぜ</t>
+          <t xml:space="preserve">あいつとの試合、組んでくれよ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.delinquent.normal[1]</t>
+          <t xml:space="preserve">S3.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6783,14 +6783,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…（沈黙）…いや、なんでもねえよ</t>
+          <t xml:space="preserve">ちょっと休ませてくれ…</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.delinquent.normal[1]</t>
+          <t xml:space="preserve">S4_direct.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6815,14 +6815,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓させてくれ。もっと強くなりてえ</t>
+          <t xml:space="preserve">不満だっつってんの。ちゃんと話し合おうぜ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.delinquent.normal[1]</t>
+          <t xml:space="preserve">S4_silent.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6847,14 +6847,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の面倒、見させてくれよ</t>
+          <t xml:space="preserve">…（沈黙）…いや、なんでもねえよ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6864,12 +6864,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.delinquent.normal[1]</t>
+          <t xml:space="preserve">S5.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6879,14 +6879,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いてて…やっちまった。すぐ戻るから</t>
+          <t xml:space="preserve">特訓させてくれ。もっと強くなりてえ</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6896,12 +6896,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.delinquent.normal[1]</t>
+          <t xml:space="preserve">S6.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6911,14 +6911,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつとはもう無理だ。何とかしてくれ</t>
+          <t xml:space="preserve">後輩の面倒、見させてくれよ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.delinquent.normal[1]</t>
+          <t xml:space="preserve">B1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6943,14 +6943,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">向こうが悪いんだろ。なんで私だけ？</t>
+          <t xml:space="preserve">いてて…やっちまった。すぐ戻るから</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.delinquent.normal[1]</t>
+          <t xml:space="preserve">B2_fighter1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6975,14 +6975,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ブランドとコラボ…？ なんか柄じゃないな。でもやる</t>
+          <t xml:space="preserve">あいつとはもう無理だ。何とかしてくれ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.delinquent.normal[1]</t>
+          <t xml:space="preserve">B2_fighter2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7007,14 +7007,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM！？ なんか恥ずかしいけど、やってやるよ</t>
+          <t xml:space="preserve">向こうが悪いんだろ。なんで私だけ？</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.delinquent.normal[1]</t>
+          <t xml:space="preserve">B4_brand.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7039,14 +7039,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンイベ！ 直接会えるのいいな</t>
+          <t xml:space="preserve">ブランドとコラボ…？ なんか柄じゃないな。でもやる</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.delinquent.normal[1]</t>
+          <t xml:space="preserve">B4_cm.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7071,14 +7071,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファッションショー…？ 歩くだけ？ まぁいいけど</t>
+          <t xml:space="preserve">CM！？ なんか恥ずかしいけど、やってやるよ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.delinquent.normal[1]</t>
+          <t xml:space="preserve">B4_fan.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7103,14 +7103,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビア…？ まぁ、やってやるか</t>
+          <t xml:space="preserve">ファンイベ！ 直接会えるのいいな</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.delinquent.normal[1]</t>
+          <t xml:space="preserve">B4_fashion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7135,14 +7135,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティ？ 面白いことしてやるよ</t>
+          <t xml:space="preserve">ファッションショー…？ 歩くだけ？ まぁいいけど</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.delinquent.normal[1]</t>
+          <t xml:space="preserve">B4_gravure.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7167,14 +7167,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">取材？ やってやるよ！</t>
+          <t xml:space="preserve">グラビア…？ まぁ、やってやるか</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7184,29 +7184,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">B4_variety.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれるなら、全力で暴れるぜ</t>
+          <t xml:space="preserve">バラエティ？ 面白いことしてやるよ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7216,29 +7216,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">B4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
+          <t xml:space="preserve">取材？ やってやるよ！</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.normal[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7263,14 +7263,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、期待しててくれよ</t>
+          <t xml:space="preserve">選んでくれるなら、全力で暴れるぜ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
@@ -7302,7 +7302,7 @@
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7327,14 +7327,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな！ガンガンやるぜ</t>
+          <t xml:space="preserve">まぁ、期待しててくれよ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
@@ -7359,14 +7359,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ…やっちまったか</t>
+          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.normal[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7376,12 +7376,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7391,14 +7391,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなんで休むの、カッコ悪いな</t>
+          <t xml:space="preserve">よろしくな！ガンガンやるぜ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7423,14 +7423,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">片付いた話を蒸し返すな。……いい加減、疲れるんだよ</t>
+          <t xml:space="preserve">ちっ…やっちまったか</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7440,12 +7440,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7455,14 +7455,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わった扱いされんのが、一番腹立つんだよ</t>
+          <t xml:space="preserve">こんなんで休むの、カッコ悪いな</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.delinquent.normal[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7487,14 +7487,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれるなら、全力で暴れるぜ</t>
+          <t xml:space="preserve">片付いた話を蒸し返すな。……いい加減、疲れるんだよ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.delinquent.normal[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7519,14 +7519,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
+          <t xml:space="preserve">終わった扱いされんのが、一番腹立つんだよ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.delinquent.normal[2]</t>
+          <t xml:space="preserve">draftInterest.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7551,14 +7551,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、期待しててくれよ</t>
+          <t xml:space="preserve">選んでくれるなら、全力で暴れるぜ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.delinquent.normal[1]</t>
+          <t xml:space="preserve">draftJoin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7583,14 +7583,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾われた借りは、リングで返す。それだけだ</t>
+          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.delinquent.normal[1]</t>
+          <t xml:space="preserve">draftJoin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7615,14 +7615,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
+          <t xml:space="preserve">まぁ、期待しててくれよ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.delinquent.normal[1]</t>
+          <t xml:space="preserve">faGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7647,14 +7647,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな！ガンガンやるぜ</t>
+          <t xml:space="preserve">拾われた借りは、リングで返す。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.delinquent.normal[1]</t>
+          <t xml:space="preserve">faSigning.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7679,14 +7679,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ…やっちまったか</t>
+          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.delinquent.normal[2]</t>
+          <t xml:space="preserve">faWelcome.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7711,14 +7711,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなんで休むの、カッコ悪いな</t>
+          <t xml:space="preserve">よろしくな！ガンガンやるぜ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.delinquent.normal[1]</t>
+          <t xml:space="preserve">injury.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7743,14 +7743,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そうか…まぁ、縁がなかったってことだろ</t>
+          <t xml:space="preserve">ちっ…やっちまったか</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.delinquent.normal[2]</t>
+          <t xml:space="preserve">injury.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7775,14 +7775,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">世話になったな。どっかで見てろよ</t>
+          <t xml:space="preserve">こんなんで休むの、カッコ悪いな</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.delinquent.normal[1]</t>
+          <t xml:space="preserve">release.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7807,14 +7807,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな。手は抜かねーから</t>
+          <t xml:space="preserve">そうか…まぁ、縁がなかったってことだろ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.delinquent.normal[1]</t>
+          <t xml:space="preserve">release.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7839,14 +7839,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よく見つけたな。損はさせねーよ</t>
+          <t xml:space="preserve">世話になったな。どっかで見てろよ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.delinquent.normal[1]</t>
+          <t xml:space="preserve">rentalGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7871,14 +7871,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…次は絶対勝つ…！</t>
+          <t xml:space="preserve">よろしくな。手は抜かねーから</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.delinquent.normal[1]</t>
+          <t xml:space="preserve">scoutGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7903,14 +7903,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛だ！まだまだ渡さねーぞ！</t>
+          <t xml:space="preserve">よく見つけたな。損はさせねーよ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.delinquent.normal[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7935,14 +7935,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそ…ベルト取られた…でも終わりじゃねえ</t>
+          <t xml:space="preserve">くそっ…次は絶対勝つ…！</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">titleDefense.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7967,14 +7967,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったぜ！チャンピオンだ！最高！</t>
+          <t xml:space="preserve">防衛だ！まだまだ渡さねーぞ！</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">titleLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7999,14 +7999,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そうか…まぁ、縁がなかったってことだろ</t>
+          <t xml:space="preserve">くそ…ベルト取られた…でも終わりじゃねえ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">titleWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8031,14 +8031,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">世話になったな。どっかで見てろよ</t>
+          <t xml:space="preserve">やったぜ！チャンピオンだ！最高！</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
@@ -8063,14 +8063,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな。手は抜かねーから</t>
+          <t xml:space="preserve">そうか…まぁ、縁がなかったってことだろ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8095,14 +8095,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…次は絶対勝つ…！</t>
+          <t xml:space="preserve">世話になったな。どっかで見てろよ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
@@ -8127,14 +8127,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛だ！まだまだ渡さねーぞ！</t>
+          <t xml:space="preserve">よろしくな。手は抜かねーから</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
@@ -8159,14 +8159,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそ…ベルト取られた…でも終わりじゃねえ</t>
+          <t xml:space="preserve">くそっ…次は絶対勝つ…！</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
@@ -8191,14 +8191,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったぜ！チャンピオンだ！最高！</t>
+          <t xml:space="preserve">防衛だ！まだまだ渡さねーぞ！</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8208,29 +8208,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">顔見るとイラつくんだよ</t>
+          <t xml:space="preserve">くそ…ベルト取られた…でも終わりじゃねえ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8240,29 +8240,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近よそよそしくねぇか…</t>
+          <t xml:space="preserve">やったぜ！チャンピオンだ！最高！</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">bond_39_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8287,14 +8287,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると肩の力が抜けるっつーか</t>
+          <t xml:space="preserve">顔見るとイラつくんだよ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.delinquent[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.delinquent[2]</t>
+          <t xml:space="preserve">bond_59_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8319,14 +8319,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ…悪くないやつだよ</t>
+          <t xml:space="preserve">最近よそよそしくねぇか…</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8351,14 +8351,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ダチだ。何があっても守ってやる</t>
+          <t xml:space="preserve">一緒にいると肩の力が抜けるっつーか</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8383,14 +8383,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう興味ねーよ</t>
+          <t xml:space="preserve">まぁ…悪くないやつだよ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">bond_80_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8415,14 +8415,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目障りなんだよ…ぶっ潰してやる</t>
+          <t xml:space="preserve">ダチだ。何があっても守ってやる</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8447,14 +8447,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対ぶっ倒す。覚悟しろ</t>
+          <t xml:space="preserve">…もう興味ねーよ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8479,14 +8479,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この勝負が全てだ。他はどうでもいい</t>
+          <t xml:space="preserve">目障りなんだよ…ぶっ潰してやる</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8511,14 +8511,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここはあたしの場所だ。誰にも渡さねぇ</t>
+          <t xml:space="preserve">絶対ぶっ倒す。覚悟しろ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.delinquent[1]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8543,14 +8543,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなとこ、もういられるか。出て行ってやる</t>
+          <t xml:space="preserve">この勝負が全てだ。他はどうでもいい</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.delinquent[1]</t>
+          <t xml:space="preserve">trust_above_75.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8575,14 +8575,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここ、ちゃんとしてんのかよ…不安になるぜ</t>
+          <t xml:space="preserve">ここは私の場所だ。誰にも渡さねぇ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8592,12 +8592,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.delinquent.normal[1]</t>
+          <t xml:space="preserve">trust_below_20.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8607,14 +8607,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたけど…あいつ、やるじゃねぇか</t>
+          <t xml:space="preserve">こんなとこ、もういられるか。出て行ってやる</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">trust_below_35.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8639,14 +8639,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合で最高の結果だ。文句ねぇだろ</t>
+          <t xml:space="preserve">ここ、ちゃんとしてんのかよ…不安になるぜ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8671,14 +8671,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ…次は絶対ぶっ倒す</t>
+          <t xml:space="preserve">負けたけど…あいつ、やるじゃねぇか</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8703,14 +8703,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったぜ。当然だろ</t>
+          <t xml:space="preserve">最高の試合で最高の結果だ。文句ねぇだろ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-01.loss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8735,14 +8735,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一本いくぞ、おら！</t>
+          <t xml:space="preserve">ちっ…次は絶対ぶっ倒す</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-01.win.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8767,14 +8767,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おい、最近の扱い何だよ…舐めてんのか</t>
+          <t xml:space="preserve">勝ったぜ。当然だろ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-02.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8799,14 +8799,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここも悪くねぇな。やる気出てきたぜ</t>
+          <t xml:space="preserve">もう一本いくぞ、おら！</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-03.down.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8831,14 +8831,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">つるむの、結構楽しいんだよな</t>
+          <t xml:space="preserve">おい、最近の扱い何だよ…舐めてんのか</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-03.up.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8863,14 +8863,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">顔が頭から離れねぇんだよ</t>
+          <t xml:space="preserve">ここも悪くねぇな。やる気出てきたぜ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-04.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8895,14 +8895,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんで出してくれねぇんだよ…腕が鳴ってんのに</t>
+          <t xml:space="preserve">つるむの、結構楽しいんだよな</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-05.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8927,14 +8927,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそ…体がついてこねぇ</t>
+          <t xml:space="preserve">顔が頭から離れねぇんだよ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-06.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8959,14 +8959,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそが…何連敗してんだよあたしは…</t>
+          <t xml:space="preserve">なんで出してくれねぇんだよ…腕が鳴ってんのに</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-07.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8991,14 +8991,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちまくってるぜ。誰か止めてみろよ</t>
+          <t xml:space="preserve">くそ…体がついてこねぇ</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-08.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9023,14 +9023,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそ、いつまで寝てりゃいいんだよ…</t>
+          <t xml:space="preserve">くそが…何連敗してんだよ私は…</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-09.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9055,14 +9055,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー、いるな。それで?……別に</t>
+          <t xml:space="preserve">勝ちまくってるぜ。誰か止めてみろよ</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-10.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9087,14 +9087,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チッ、終わっちまったか。まぁ上等だ</t>
+          <t xml:space="preserve">くそ、いつまで寝てりゃいいんだよ…</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9104,29 +9104,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-11.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体ガタガタだけどよ。最後だ、引けるわけねえだろ</t>
+          <t xml:space="preserve">あー、いるな。それで？……別に</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9136,29 +9136,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.normal[2]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">傷だらけ上等。この一戦、あたしが全部背負ってやる</t>
+          <t xml:space="preserve">チッ、終わっちまったか。まぁ上等だ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9173,7 +9173,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.normal[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9183,14 +9183,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰だ? 何人来ようが、あたしがここで止めてやる</t>
+          <t xml:space="preserve">身体ガタガタだけどよ。最後だ、引けるわけねえだろ</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.normal[2]</t>
+          <t xml:space="preserve">preFinal.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9215,14 +9215,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリング、通れると思ってんのか。かかってこいよ</t>
+          <t xml:space="preserve">傷だらけ上等。この一戦、私が全部背負ってやる</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.delinquent.normal[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9247,14 +9247,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人潰した。…はぁ…まだ立ってんだよ。次、さっさと出てこいや</t>
+          <t xml:space="preserve">相手は誰だ？ 何人来ようが、私がここで止めてやる</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.delinquent.normal[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9279,14 +9279,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わってねえぞ。息? 上がってるけど関係ねえ。次、来い</t>
+          <t xml:space="preserve">このリング、通れると思ってんのか。かかってこいよ</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9296,12 +9296,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.normal[1]</t>
+          <t xml:space="preserve">survivor.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9311,14 +9311,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人でもぎ取った勝ちだ。あたし一人の手柄じゃねえよ</t>
+          <t xml:space="preserve">一人潰した。…はぁ…まだ立ってんだよ。次、さっさと出てこいや</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.normal[2]</t>
+          <t xml:space="preserve">survivor.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9343,14 +9343,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれたから、あたしはここにいる。それだけだろ</t>
+          <t xml:space="preserve">まだ終わってねえぞ。息? 上がってるけど関係ねえ。次、来い</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.delinquent.normal[1]</t>
+          <t xml:space="preserve">champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9375,14 +9375,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPったって、団体が負けてちゃ意味ねえよ。次は全員で勝つ</t>
+          <t xml:space="preserve">三人でもぎ取った勝ちだ。私一人の手柄じゃねえよ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.delinquent.normal[2]</t>
+          <t xml:space="preserve">champion.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9407,14 +9407,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞はもらっとく。けど、次は優勝旗も一緒にだ</t>
+          <t xml:space="preserve">仲間が繋いでくれたから、私はここにいる。それだけだろ</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.delinquent.normal[1]</t>
+          <t xml:space="preserve">defiant.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9439,14 +9439,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ようが関係ねえ。全員倒して、最後に立ってんのがあたしだ</t>
+          <t xml:space="preserve">MVPったって、団体が負けてちゃ意味ねえよ。次は全員で勝つ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.delinquent.normal[2]</t>
+          <t xml:space="preserve">defiant.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9471,14 +9471,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足ガクガクだけどよ、膝はつかなかった。それが全部だろ</t>
+          <t xml:space="preserve">この賞はもらっとく。けど、次は優勝旗も一緒にだ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9488,12 +9488,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.normal[1]</t>
+          <t xml:space="preserve">gauntlet.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9503,14 +9503,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テッペン獲ったぜ！ でもまだ上がある</t>
+          <t xml:space="preserve">何人来ようが関係ねえ。全員倒して、最後に立ってんのが私だ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.normal[2]</t>
+          <t xml:space="preserve">gauntlet.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9535,14 +9535,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝…悪くねえな。もっと強くなってやる</t>
+          <t xml:space="preserve">足ガクガクだけどよ、膝はつかなかった。それが全部だろ</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.delinquent.normal[1]</t>
+          <t xml:space="preserve">champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9567,14 +9567,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…次は絶対負けねえ</t>
+          <t xml:space="preserve">テッペン獲ったぜ！ でもまだ上がある</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.delinquent.normal[2]</t>
+          <t xml:space="preserve">champion.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9599,14 +9599,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなとこで終わってたまるか…</t>
+          <t xml:space="preserve">優勝…悪くねえな。もっと強くなってやる</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">postLose.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9631,14 +9631,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっし、一丁上がりだ。次もブチかます</t>
+          <t xml:space="preserve">くそっ…次は絶対負けねえ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.delinquent.normal[2]</t>
+          <t xml:space="preserve">postLose.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9663,14 +9663,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ止まんねえぞ</t>
+          <t xml:space="preserve">こんなとこで終わってたまるか…</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9695,14 +9695,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあまあやれたな。次はもっと暴れてやるぜ</t>
+          <t xml:space="preserve">おっし、一丁上がりだ。次もブチかます</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.delinquent.normal[2]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9727,14 +9727,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悪くねえ結果だ</t>
+          <t xml:space="preserve">まだまだ止まんねえぞ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.normal[1]</t>
+          <t xml:space="preserve">postWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9759,14 +9759,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝だぜ。最後もぶっ潰してやる</t>
+          <t xml:space="preserve">まあまあやれたな。次はもっと暴れてやるぜ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.normal[2]</t>
+          <t xml:space="preserve">postWin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9791,14 +9791,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たんだ。もう引けねえ</t>
+          <t xml:space="preserve">悪くねえ結果だ</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.normal[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9823,14 +9823,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっ潰す。それだけだ</t>
+          <t xml:space="preserve">決勝だぜ。最後もぶっ潰してやる</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.normal[2]</t>
+          <t xml:space="preserve">preFinal.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9855,14 +9855,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手とか関係ねえ。全力で行くだけだ</t>
+          <t xml:space="preserve">ここまで来たんだ。もう引けねえ</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.delinquent.normal[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9887,14 +9887,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おう、出てやるよ。覚悟しとけ</t>
+          <t xml:space="preserve">ぶっ潰す。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.delinquent.normal[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9919,14 +9919,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員まとめてかかって来いってんだ</t>
+          <t xml:space="preserve">相手とか関係ねえ。全力で行くだけだ</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9936,12 +9936,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">summon.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9951,14 +9951,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けねーぞ。かかってこい</t>
+          <t xml:space="preserve">おう、出てやるよ。覚悟しとけ</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9968,12 +9968,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">summon.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9983,14 +9983,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうだ……！ これがウチの団体の力だ……！</t>
+          <t xml:space="preserve">全員まとめてかかって来いってんだ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.normal[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10000,12 +10000,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10015,14 +10015,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺん獲ったぞ……！ 見てたか……！</t>
+          <t xml:space="preserve">今日は負けねーぞ。かかってこい</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
@@ -10047,14 +10047,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おい、聞いたぜ？ 弱小団体がイキってるってな</t>
+          <t xml:space="preserve">どうだ……！ これがウチの団体の力だ……！</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.normal[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
@@ -10079,14 +10079,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ボコボコにしてやっから、覚悟しとけ</t>
+          <t xml:space="preserve">てっぺん獲ったぞ……！ 見てたか……！</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
@@ -10111,14 +10111,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、逃げやがった。ビビりが</t>
+          <t xml:space="preserve">おい、聞いたぜ？ 弱小団体がイキってるってな</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.normal[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
@@ -10143,14 +10143,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チキンかよ。次はねえぞ</t>
+          <t xml:space="preserve">ボコボコにしてやっから、覚悟しとけ</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.normal[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10175,14 +10175,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…やられた…。次は絶対ぶっ潰す</t>
+          <t xml:space="preserve">はっ、逃げやがった。ビビりが</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.normal[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.delinquent.normal[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10207,14 +10207,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この借り…倍にして返してやるからな</t>
+          <t xml:space="preserve">チキンかよ。次はねえぞ</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.delinquent.normal[1]</t>
+          <t xml:space="preserve">result_lose.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10239,14 +10239,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうだ、これがウチの実力だ。舐めんなよ</t>
+          <t xml:space="preserve">くそっ…やられた…。次は絶対ぶっ潰す</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.delinquent.normal[2]</t>
+          <t xml:space="preserve">result_lose.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10271,14 +10271,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったぜ。ま、当然だけどな</t>
+          <t xml:space="preserve">この借り…倍にして返してやるからな</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">result_win.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10303,14 +10303,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">舐めんなよ。うちの団体はこんなもんじゃねえ</t>
+          <t xml:space="preserve">どうだ、これがウチの実力だ。舐めんなよ</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">result_win.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10335,14 +10335,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったぜ。文句あるか？</t>
+          <t xml:space="preserve">勝ったぜ。ま、当然だけどな</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[3]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10367,14 +10367,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽勝だぜ。次もかかってこいよ</t>
+          <t xml:space="preserve">舐めんなよ。うちの団体はこんなもんじゃねえ</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.delinquent.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10384,29 +10384,29 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やってやったぜ！最高だ！</t>
+          <t xml:space="preserve">勝ったぜ。文句あるか？</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10416,59 +10416,123 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[3]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾われた借りは、リングで返す。それだけだ</t>
+          <t xml:space="preserve">楽勝だぜ。次もかかってこいよ</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やってやったぜ！最高だ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">拾われた借りは、リングで返す。それだけだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="40" customHeight="1">
+      <c r="A318" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.delinquent.normal[1]</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr" s="2">
+      <c r="B318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr" s="12">
+      <c r="D318" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr" s="2">
+      <c r="E318" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr" s="3">
+      <c r="F318" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">よく見つけたな。損はさせねーよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H316"/>
+  <autoFilter ref="A1:H318"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/ヤンキー×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/ヤンキー×ノーマル.xlsx
@@ -328,7 +328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H318"/>
+  <dimension ref="A1:H325"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4450,7 +4450,7 @@
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.delinquent.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.delinquent.normal[1]</t>
+          <t xml:space="preserve">decline_accept.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4475,14 +4475,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">サンキュ、社長。ちゃんと働くからよ。</t>
+          <t xml:space="preserve">うん、それでいい。……変に情をかけられるほうが、よっぽど堪えるからさ。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.delinquent.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.delinquent.normal[1]</t>
+          <t xml:space="preserve">decline_hold.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4507,14 +4507,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まー上がるだけマシか。サンキュ。</t>
+          <t xml:space="preserve">は……据え置き？ ……なんでだよ。……いや、いい。働いて返す。それでチャラにさせて。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.delinquent.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.delinquent.normal[1]</t>
+          <t xml:space="preserve">decline_open.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4539,14 +4539,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……チッ。まあ分かったよ。</t>
+          <t xml:space="preserve">{tenure}下がるのか。……ま、去年の私を見てりゃ、そういう話にもなるよな。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.delinquent.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.delinquent.normal[1]</t>
+          <t xml:space="preserve">decline_strict.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4571,14 +4571,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ちょっといいか。{tenure}{record}給料の話なんだけどさ。もうちょい出してくんねーの？</t>
+          <t xml:space="preserve">……そこまでやるんだ。……いいよ、覚えとく。数字で見られてんなら、数字で返すだけ。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.delinquent.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.delinquent.normal[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4603,14 +4603,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……マジかよ。……まあいいけどさ。</t>
+          <t xml:space="preserve">そう、それでいい。……自分で言った額で立つほうが、背筋が伸びるからさ。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.delinquent.normal[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4635,14 +4635,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、話は手短にするっす。辞めます。もう決めました。</t>
+          <t xml:space="preserve">……いや、下げろって言ったんだけど。……ったく。……そういうとこ、嫌いじゃないよ。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.normal[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.delinquent.normal[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4667,14 +4667,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">世話になりました。でも、もうここじゃ続けられないっす。</t>
+          <t xml:space="preserve">社長、先に言っとく。{tenure}私の全盛期はもう過ぎた。下げていいよ。数字は嘘つかねえもんな。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.delinquent.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.delinquent.normal[1]</t>
+          <t xml:space="preserve">raise_accept.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4699,14 +4699,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">聞いてくれんのか。{record}正直、もっと面白えとこでやりてーんだよ。</t>
+          <t xml:space="preserve">サンキュ、社長。ちゃんと働くからよ。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.delinquent.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.delinquent.normal[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4731,14 +4731,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}悪いけど、もうここ出るわ。</t>
+          <t xml:space="preserve">まー上がるだけマシか。サンキュ。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.delinquent.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.delinquent.normal[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4763,14 +4763,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……おう。{tenure_farewell}{rivalry}じゃーな。</t>
+          <t xml:space="preserve">……チッ。まあ分かったよ。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.delinquent.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.delinquent.normal[1]</t>
+          <t xml:space="preserve">raise_open.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4795,14 +4795,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪いけど、もう決めたんだよ。気持ちは変わらねー。</t>
+          <t xml:space="preserve">社長、ちょっといいか。{tenure}{record}給料の話なんだけどさ。もうちょい出してくんねーの？</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.delinquent.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.delinquent.normal[1]</t>
+          <t xml:space="preserve">raise_refuse.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4827,402 +4827,402 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……マジかよ。そこまで言うなら、もうちょいいてやるか。</t>
+          <t xml:space="preserve">……マジかよ。……まあいいけどさ。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、話は手短にするっす。辞めます。もう決めました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.delinquent.normal[2]</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.delinquent.normal[2]</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">世話になりました。でも、もうここじゃ続けられないっす。</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">聞いてくれんのか。{record}正直、もっと面白えとこでやりてーんだよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}悪いけど、もうここ出るわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……おう。{tenure_farewell}{rivalry}じゃーな。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……悪いけど、もう決めたんだよ。気持ちは変わらねー。</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="40" customHeight="1">
+      <c r="A147" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……マジかよ。そこまで言うなら、もうちょいいてやるか。</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="40" customHeight="1">
+      <c r="A148" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.delinquent.normal[1]</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr" s="2">
+      <c r="B148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr" s="12">
+      <c r="D148" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.delinquent.normal[1]</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr" s="2">
+      <c r="E148" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr" s="3">
+      <c r="F148" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">悪いな、話を聞く気にならねぇ。
 今の仲間を裏切るわけにはいかねぇから</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="40" customHeight="1">
-      <c r="A142" t="inlineStr" s="15">
+    <row r="149" ht="40" customHeight="1">
+      <c r="A149" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.delinquent.normal[1]</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr" s="2">
+      <c r="B149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr" s="12">
+      <c r="D149" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.delinquent.normal[1]</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr" s="2">
+      <c r="E149" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr" s="3">
+      <c r="F149" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">悪ぃけど、今回はパスだ。
 縁があればまたな</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="40" customHeight="1">
-      <c r="A143" t="inlineStr" s="15">
+    <row r="150" ht="40" customHeight="1">
+      <c r="A150" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.delinquent.normal[1]</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr" s="2">
+      <c r="B150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr" s="12">
+      <c r="D150" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.delinquent.normal[1]</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr" s="2">
+      <c r="E150" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr" s="3">
+      <c r="F150" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">私を引き抜くってか？
 …条件次第だな</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="40" customHeight="1">
-      <c r="A144" t="inlineStr" s="15">
+    <row r="151" ht="40" customHeight="1">
+      <c r="A151" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.delinquent.normal[1]</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr" s="2">
+      <c r="B151" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr" s="12">
+      <c r="D151" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.delinquent.normal[1]</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr" s="2">
+      <c r="E151" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr" s="3">
+      <c r="F151" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…わかった、行くぜ。
 実力で居場所作ってやるよ</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="40" customHeight="1">
-      <c r="A145" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.delinquent.normal[1]</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">黙ってたけど、もう限界だっつーの。</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="40" customHeight="1">
-      <c r="A146" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.delinquent.normal[1]</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">おっしゃ！ なんか壁越えた気がするぜ！</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="40" customHeight="1">
-      <c r="A147" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES.delinquent.normal[1]</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">（…なんだ、この感覚。体が勝手に動きやがる——）</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="40" customHeight="1">
-      <c r="A148" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.delinquent.normal[1]</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cap_reached.delinquent.normal[1]</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…ちっ、ここが天井か。でも悪くねえ</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="40" customHeight="1">
-      <c r="A149" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.delinquent.normal[1]</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_elite.delinquent.normal[1]</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ここまで来たら、もう誰にも止められねえ</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="40" customHeight="1">
-      <c r="A150" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.delinquent.normal[1]</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_growth.delinquent.normal[1]</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">おっ、ちょっとは強くなったじゃん</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="40" customHeight="1">
-      <c r="A151" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.delinquent.normal[1]</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_legend.delinquent.normal[1]</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">はは…マジかよ、こんなとこまで来ちまった</t>
-        </is>
-      </c>
-    </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.delinquent.normal[1]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっ、知名度上がってんじゃん</t>
+          <t xml:space="preserve">黙ってたけど、もう限界だっつーの。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.delinquent.normal[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5247,14 +5247,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すっげえ声援だな…やべえ、ちょっと鳥肌立った</t>
+          <t xml:space="preserve">おっしゃ！ なんか壁越えた気がするぜ！</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
@@ -5279,14 +5279,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何のために闘ってんだよ…もうわかんねー</t>
+          <t xml:space="preserve">（…なんだ、この感覚。体が勝手に動きやがる——）</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">cap_reached.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5311,14 +5311,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだやれる…やってやるよ</t>
+          <t xml:space="preserve">…ちっ、ここが天井か。でも悪くねえ</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">ovr_elite.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5343,14 +5343,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと…やっと戻ってこれたぜ</t>
+          <t xml:space="preserve">ここまで来たら、もう誰にも止められねえ</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.delinquent.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.delinquent.normal[1]</t>
+          <t xml:space="preserve">ovr_growth.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5375,14 +5375,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの負けから…何かおかしいんだよ</t>
+          <t xml:space="preserve">おっ、ちょっとは強くなったじゃん</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.delinquent.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5392,12 +5392,12 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.delinquent.normal[1]</t>
+          <t xml:space="preserve">ovr_legend.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5407,14 +5407,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体は治ったはずだろ…なんで動けねーんだ</t>
+          <t xml:space="preserve">はは…マジかよ、こんなとこまで来ちまった</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.delinquent.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.delinquent.normal[1]</t>
+          <t xml:space="preserve">pop_growth.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5439,14 +5439,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">戻ってきたのに…ビビってんのかよ、私</t>
+          <t xml:space="preserve">おっ、知名度上がってんじゃん</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.delinquent.normal[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5456,12 +5456,12 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.delinquent.normal[1]</t>
+          <t xml:space="preserve">pop_star.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5471,14 +5471,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治ったっつーのに…気力が戻んねー</t>
+          <t xml:space="preserve">すっげえ声援だな…やべえ、ちょっと鳥肌立った</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.delinquent.normal[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5488,29 +5488,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うちの団体をなめるなって、ちゃんと教えてやったよ。</t>
+          <t xml:space="preserve">何のために闘ってんだよ…もうわかんねー</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.delinquent.normal[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5520,29 +5520,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合はヤバかった。体が勝手に動いてた。あいつとじゃなきゃ無理だった</t>
+          <t xml:space="preserve">まだやれる…やってやるよ</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.delinquent.normal[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5552,29 +5552,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルト欲しいやつ、いくらでもかかってこい。全員叩き返す</t>
+          <t xml:space="preserve">やっと…やっと戻ってこれたぜ</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.delinquent.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5584,29 +5584,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.delinquent.normal[1]</t>
+          <t xml:space="preserve">defeat.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まさかこんな名誉あるもんもらえる日が来るとはな…。全部、リングがくれたもんだ</t>
+          <t xml:space="preserve">あの負けから…何かおかしいんだよ</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.delinquent.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5616,29 +5616,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.delinquent.normal[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっ、マジで？ やっべ、嬉しい</t>
+          <t xml:space="preserve">体は治ったはずだろ…なんで動けねーんだ</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.delinquent.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5648,29 +5648,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.delinquent.normal[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間ずっと全力だった。手抜いた日なんか一日もねえよ</t>
+          <t xml:space="preserve">戻ってきたのに…ビビってんのかよ、私</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.delinquent.normal[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5680,29 +5680,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.delinquent.normal[1]</t>
+          <t xml:space="preserve">penalty_end.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直ビビってる。こんなちゃんとした賞もらったの初めてだ…来年も取る</t>
+          <t xml:space="preserve">怪我は治ったっつーのに…気力が戻んねー</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.delinquent.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.delinquent.normal[1]</t>
+          <t xml:space="preserve">autumnWarChampion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5727,14 +5727,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒と決めたことをやっただけだ。文句あるやつはかかってきな。</t>
+          <t xml:space="preserve">うちの団体をなめるなって、ちゃんと教えてやったよ。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5744,12 +5744,12 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">bestMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5759,14 +5759,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おい、ここがドームってやつか。デカいな</t>
+          <t xml:space="preserve">あの試合はヤバかった。体が勝手に動いてた。あいつとじゃなきゃ無理だった</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5791,14 +5791,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まぁ、悪くねえ気分だ</t>
+          <t xml:space="preserve">このベルト欲しいやつ、いくらでもかかってこい。全員叩き返す</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.normal[3]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[3]</t>
+          <t xml:space="preserve">hallOfFame.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5823,14 +5823,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふん、やってやるよ。ドームだろうが同じだろ</t>
+          <t xml:space="preserve">まさかこんな名誉あるもんもらえる日が来るとはな…。全部、リングがくれたもんだ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">mediaAward.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5855,14 +5855,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…マジかよ、満員だって？</t>
+          <t xml:space="preserve">えっ、マジで？ やっべ、嬉しい</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">mvp.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5887,14 +5887,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっそ、これがドーム満員ってやつか…</t>
+          <t xml:space="preserve">一年間ずっと全力だった。手抜いた日なんか一日もねえよ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.normal[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[3]</t>
+          <t xml:space="preserve">rookie.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5919,14 +5919,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くねえな。…全然悪くねえ</t>
+          <t xml:space="preserve">正直ビビってる。こんなちゃんとした賞もらったの初めてだ…来年も取る</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5936,29 +5936,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.delinquent.normal[1]</t>
+          <t xml:space="preserve">springTagChampion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか最近、体の動きキレてね？</t>
+          <t xml:space="preserve">相棒と決めたことをやっただけだ。文句あるやつはかかってきな。</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.normal[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5968,29 +5968,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.delinquent.normal[2]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと感覚掴めてきたっぽい</t>
+          <t xml:space="preserve">おい、ここがドームってやつか。デカいな</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.delinquent.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6000,29 +6000,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつと一緒だと楽しいんだよな</t>
+          <t xml:space="preserve">…まぁ、悪くねえ気分だ</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.delinquent.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6032,29 +6032,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[3]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっとダルいだけだって。すぐ戻る</t>
+          <t xml:space="preserve">ふん、やってやるよ。ドームだろうが同じだろ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.delinquent.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6064,29 +6064,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれるやつがいるってのは…悪くねえな</t>
+          <t xml:space="preserve">…マジかよ、満員だって？</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.delinquent.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6096,29 +6096,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もういいわ。勝手にする</t>
+          <t xml:space="preserve">くっそ、これがドーム満員ってやつか…</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.delinquent.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6128,29 +6128,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[3]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…別に。何でもねーよ</t>
+          <t xml:space="preserve">…悪くねえな。…全然悪くねえ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.delinquent.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.delinquent.normal[1]</t>
+          <t xml:space="preserve">N1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6175,14 +6175,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チッ</t>
+          <t xml:space="preserve">なんか最近、体の動きキレてね？</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.delinquent.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6192,29 +6192,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.delinquent.normal[1]</t>
+          <t xml:space="preserve">N1.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">は？ ケチくさ。いらねーよ、こんなん</t>
+          <t xml:space="preserve">やっと感覚掴めてきたっぽい</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.delinquent.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6224,29 +6224,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.delinquent.normal[1]</t>
+          <t xml:space="preserve">N2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、マジ？ ありがとな！</t>
+          <t xml:space="preserve">あいつと一緒だと楽しいんだよな</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.delinquent.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6256,29 +6256,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.delinquent.normal[1]</t>
+          <t xml:space="preserve">N3.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿！ ガンガンやるぞ！</t>
+          <t xml:space="preserve">ちょっとダルいだけだって。すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.delinquent.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6288,29 +6288,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.delinquent.normal[1]</t>
+          <t xml:space="preserve">N4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…アンタに言われると、やんなきゃって思うんだよ</t>
+          <t xml:space="preserve">応援してくれるやつがいるってのは…悪くねえな</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.delinquent.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.delinquent.normal[1]</t>
+          <t xml:space="preserve">N5_low.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…サンキュ。もうちょいやってみるわ</t>
+          <t xml:space="preserve">…もういいわ。勝手にする</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.delinquent.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6352,29 +6352,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.delinquent.normal[1]</t>
+          <t xml:space="preserve">N5_warning.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ？ やってやるよ！</t>
+          <t xml:space="preserve">…別に。何でもねーよ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.delinquent.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6384,29 +6384,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.delinquent.normal[1]</t>
+          <t xml:space="preserve">G1.voice.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いえーい！カンパーイ！</t>
+          <t xml:space="preserve">…チッ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.delinquent.normal[1]</t>
+          <t xml:space="preserve">bonus_insult.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6431,14 +6431,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">サンキュ！ちょっと休んでくるわ</t>
+          <t xml:space="preserve">は？ ケチくさ。いらねーよ、こんなん</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.delinquent.normal[1]</t>
+          <t xml:space="preserve">bonus.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6463,14 +6463,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">サンキュ。早く治してリング戻るわ</t>
+          <t xml:space="preserve">お、マジ？ ありがとな！</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.delinquent.normal[1]</t>
+          <t xml:space="preserve">camp.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6495,14 +6495,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっしゃ、ガンガンやるぞ！</t>
+          <t xml:space="preserve">合宿！ ガンガンやるぞ！</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.delinquent.normal[1]</t>
+          <t xml:space="preserve">encourage_high_trust.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6527,14 +6527,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ出れんの？ やるやる！</t>
+          <t xml:space="preserve">…アンタに言われると、やんなきゃって思うんだよ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.delinquent.normal[1]</t>
+          <t xml:space="preserve">encourage.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6559,14 +6559,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しいスカウトの話、来てるみたいっすよ</t>
+          <t xml:space="preserve">…サンキュ。もうちょいやってみるわ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.delinquent.normal[1]</t>
+          <t xml:space="preserve">media.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6591,14 +6591,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所から話来てんだけど</t>
+          <t xml:space="preserve">テレビ？ やってやるよ！</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6608,12 +6608,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.delinquent.normal[1]</t>
+          <t xml:space="preserve">party.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6623,14 +6623,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習？やる意味あんの？出してもらえねぇんじゃ同じだろ</t>
+          <t xml:space="preserve">いえーい！カンパーイ！</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.delinquent.normal[1]</t>
+          <t xml:space="preserve">refresh_leave.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6655,14 +6655,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「マジふざけんな」とロッカーを蹴る音が聞こえてきた）</t>
+          <t xml:space="preserve">サンキュ！ちょっと休んでくるわ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.delinquent.normal[1]</t>
+          <t xml:space="preserve">special_treatment.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6687,14 +6687,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「もう我慢の限界」と不穏な投稿）</t>
+          <t xml:space="preserve">サンキュ。早く治してリング戻るわ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.delinquent.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.delinquent.normal[1]</t>
+          <t xml:space="preserve">trainer.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6719,14 +6719,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タイトルマッチ、組んでくれよ</t>
+          <t xml:space="preserve">おっしゃ、ガンガンやるぞ！</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.delinquent.normal[1]</t>
+          <t xml:space="preserve">E1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6751,14 +6751,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつとの試合、組んでくれよ</t>
+          <t xml:space="preserve">テレビ出れんの？ やるやる！</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.delinquent.normal[1]</t>
+          <t xml:space="preserve">E4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6783,14 +6783,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと休ませてくれ…</t>
+          <t xml:space="preserve">新しいスカウトの話、来てるみたいっすよ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.delinquent.normal[1]</t>
+          <t xml:space="preserve">E6.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6815,14 +6815,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不満だっつってんの。ちゃんと話し合おうぜ</t>
+          <t xml:space="preserve">他所から話来てんだけど</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.delinquent.normal[1]</t>
+          <t xml:space="preserve">S_boycott.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6847,14 +6847,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…（沈黙）…いや、なんでもねえよ</t>
+          <t xml:space="preserve">練習？やる意味あんの？出してもらえねぇんじゃ同じだろ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.delinquent.normal[1]</t>
+          <t xml:space="preserve">S_grumble.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6879,14 +6879,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓させてくれ。もっと強くなりてえ</t>
+          <t xml:space="preserve">（「マジふざけんな」とロッカーを蹴る音が聞こえてきた）</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.delinquent.normal[1]</t>
+          <t xml:space="preserve">S_sns.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6911,14 +6911,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の面倒、見させてくれよ</t>
+          <t xml:space="preserve">（SNSに「もう我慢の限界」と不穏な投稿）</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.delinquent.normal[1]</t>
+          <t xml:space="preserve">S1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6943,14 +6943,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いてて…やっちまった。すぐ戻るから</t>
+          <t xml:space="preserve">タイトルマッチ、組んでくれよ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.delinquent.normal[1]</t>
+          <t xml:space="preserve">S2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6975,14 +6975,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつとはもう無理だ。何とかしてくれ</t>
+          <t xml:space="preserve">あいつとの試合、組んでくれよ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6992,12 +6992,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.delinquent.normal[1]</t>
+          <t xml:space="preserve">S3.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7007,14 +7007,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">向こうが悪いんだろ。なんで私だけ？</t>
+          <t xml:space="preserve">ちょっと休ませてくれ…</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.delinquent.normal[1]</t>
+          <t xml:space="preserve">S4_direct.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7039,14 +7039,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ブランドとコラボ…？ なんか柄じゃないな。でもやる</t>
+          <t xml:space="preserve">不満だっつってんの。ちゃんと話し合おうぜ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7056,12 +7056,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.delinquent.normal[1]</t>
+          <t xml:space="preserve">S4_silent.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7071,14 +7071,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM！？ なんか恥ずかしいけど、やってやるよ</t>
+          <t xml:space="preserve">…（沈黙）…いや、なんでもねえよ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7088,12 +7088,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.delinquent.normal[1]</t>
+          <t xml:space="preserve">S5.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7103,14 +7103,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンイベ！ 直接会えるのいいな</t>
+          <t xml:space="preserve">特訓させてくれ。もっと強くなりてえ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.delinquent.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.delinquent.normal[1]</t>
+          <t xml:space="preserve">S6.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7135,14 +7135,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファッションショー…？ 歩くだけ？ まぁいいけど</t>
+          <t xml:space="preserve">後輩の面倒、見させてくれよ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.delinquent.normal[1]</t>
+          <t xml:space="preserve">B1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7167,14 +7167,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビア…？ まぁ、やってやるか</t>
+          <t xml:space="preserve">いてて…やっちまった。すぐ戻るから</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.delinquent.normal[1]</t>
+          <t xml:space="preserve">B2_fighter1.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7199,14 +7199,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティ？ 面白いことしてやるよ</t>
+          <t xml:space="preserve">あいつとはもう無理だ。何とかしてくれ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.delinquent.normal[1]</t>
+          <t xml:space="preserve">B2_fighter2.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7231,14 +7231,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">取材？ やってやるよ！</t>
+          <t xml:space="preserve">向こうが悪いんだろ。なんで私だけ？</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7248,29 +7248,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">B4_brand.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれるなら、全力で暴れるぜ</t>
+          <t xml:space="preserve">ブランドとコラボ…？ なんか柄じゃないな。でもやる</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7280,29 +7280,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">B4_cm.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
+          <t xml:space="preserve">CM！？ なんか恥ずかしいけど、やってやるよ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.normal[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7312,29 +7312,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">B4_fan.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、期待しててくれよ</t>
+          <t xml:space="preserve">ファンイベ！ 直接会えるのいいな</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7344,29 +7344,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">B4_fashion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
+          <t xml:space="preserve">ファッションショー…？ 歩くだけ？ まぁいいけど</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7376,29 +7376,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">B4_gravure.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな！ガンガンやるぜ</t>
+          <t xml:space="preserve">グラビア…？ まぁ、やってやるか</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7408,29 +7408,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">B4_variety.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ…やっちまったか</t>
+          <t xml:space="preserve">バラエティ？ 面白いことしてやるよ</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.normal[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">B4.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなんで休むの、カッコ悪いな</t>
+          <t xml:space="preserve">取材？ やってやるよ！</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7487,14 +7487,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">片付いた話を蒸し返すな。……いい加減、疲れるんだよ</t>
+          <t xml:space="preserve">選んでくれるなら、全力で暴れるぜ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7519,14 +7519,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わった扱いされんのが、一番腹立つんだよ</t>
+          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7551,14 +7551,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれるなら、全力で暴れるぜ</t>
+          <t xml:space="preserve">まぁ、期待しててくれよ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7590,7 +7590,7 @@
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.normal[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.delinquent.normal[2]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7615,14 +7615,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、期待しててくれよ</t>
+          <t xml:space="preserve">よろしくな！ガンガンやるぜ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7632,12 +7632,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7647,14 +7647,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾われた借りは、リングで返す。それだけだ</t>
+          <t xml:space="preserve">ちっ…やっちまったか</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7679,14 +7679,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
+          <t xml:space="preserve">こんなんで休むの、カッコ悪いな</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.delinquent.normal[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7711,14 +7711,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな！ガンガンやるぜ</t>
+          <t xml:space="preserve">片付いた話を蒸し返すな。……いい加減、疲れるんだよ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.delinquent.normal[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7743,14 +7743,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ…やっちまったか</t>
+          <t xml:space="preserve">終わった扱いされんのが、一番腹立つんだよ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.delinquent.normal[2]</t>
+          <t xml:space="preserve">draftInterest.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7775,14 +7775,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなんで休むの、カッコ悪いな</t>
+          <t xml:space="preserve">選んでくれるなら、全力で暴れるぜ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.delinquent.normal[1]</t>
+          <t xml:space="preserve">draftJoin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7807,14 +7807,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そうか…まぁ、縁がなかったってことだろ</t>
+          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.delinquent.normal[2]</t>
+          <t xml:space="preserve">draftJoin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7839,14 +7839,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">世話になったな。どっかで見てろよ</t>
+          <t xml:space="preserve">まぁ、期待しててくれよ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.delinquent.normal[1]</t>
+          <t xml:space="preserve">faGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7871,14 +7871,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな。手は抜かねーから</t>
+          <t xml:space="preserve">拾われた借りは、リングで返す。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.delinquent.normal[1]</t>
+          <t xml:space="preserve">faSigning.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7903,14 +7903,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よく見つけたな。損はさせねーよ</t>
+          <t xml:space="preserve">よろしくな。暴れさせてもらうぜ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.delinquent.normal[1]</t>
+          <t xml:space="preserve">faWelcome.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7935,14 +7935,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…次は絶対勝つ…！</t>
+          <t xml:space="preserve">よろしくな！ガンガンやるぜ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.delinquent.normal[1]</t>
+          <t xml:space="preserve">injury.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7967,14 +7967,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛だ！まだまだ渡さねーぞ！</t>
+          <t xml:space="preserve">ちっ…やっちまったか</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.delinquent.normal[1]</t>
+          <t xml:space="preserve">injury.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7999,14 +7999,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそ…ベルト取られた…でも終わりじゃねえ</t>
+          <t xml:space="preserve">こんなんで休むの、カッコ悪いな</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">release.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8031,14 +8031,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったぜ！チャンピオンだ！最高！</t>
+          <t xml:space="preserve">そうか…まぁ、縁がなかったってことだろ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">release.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8063,14 +8063,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そうか…まぁ、縁がなかったってことだろ</t>
+          <t xml:space="preserve">世話になったな。どっかで見てろよ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">rentalGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8095,14 +8095,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">世話になったな。どっかで見てろよ</t>
+          <t xml:space="preserve">よろしくな。手は抜かねーから</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">scoutGreeting.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8127,14 +8127,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくな。手は抜かねーから</t>
+          <t xml:space="preserve">よく見つけたな。損はさせねーよ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8166,7 +8166,7 @@
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">titleDefense.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8198,7 +8198,7 @@
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">titleLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8230,7 +8230,7 @@
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">titleWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8262,7 +8262,7 @@
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8272,29 +8272,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">顔見るとイラつくんだよ</t>
+          <t xml:space="preserve">そうか…まぁ、縁がなかったってことだろ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8304,29 +8304,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近よそよそしくねぇか…</t>
+          <t xml:space="preserve">世話になったな。どっかで見てろよ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8336,29 +8336,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると肩の力が抜けるっつーか</t>
+          <t xml:space="preserve">よろしくな。手は抜かねーから</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.delinquent[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8368,29 +8368,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.delinquent[2]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ…悪くないやつだよ</t>
+          <t xml:space="preserve">くそっ…次は絶対勝つ…！</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8400,29 +8400,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ダチだ。何があっても守ってやる</t>
+          <t xml:space="preserve">防衛だ！まだまだ渡さねーぞ！</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8432,29 +8432,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう興味ねーよ</t>
+          <t xml:space="preserve">くそ…ベルト取られた…でも終わりじゃねえ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8464,29 +8464,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目障りなんだよ…ぶっ潰してやる</t>
+          <t xml:space="preserve">やったぜ！チャンピオンだ！最高！</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">bond_39_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8511,14 +8511,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対ぶっ倒す。覚悟しろ</t>
+          <t xml:space="preserve">顔見るとイラつくんだよ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.delinquent[1]</t>
+          <t xml:space="preserve">bond_59_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8543,14 +8543,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この勝負が全てだ。他はどうでもいい</t>
+          <t xml:space="preserve">最近よそよそしくねぇか…</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.delinquent[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8575,14 +8575,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここは私の場所だ。誰にも渡さねぇ</t>
+          <t xml:space="preserve">一緒にいると肩の力が抜けるっつーか</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.delinquent[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.delinquent[2]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8607,14 +8607,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなとこ、もういられるか。出て行ってやる</t>
+          <t xml:space="preserve">まぁ…悪くないやつだよ</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.delinquent[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.delinquent[1]</t>
+          <t xml:space="preserve">bond_80_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8639,14 +8639,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここ、ちゃんとしてんのかよ…不安になるぜ</t>
+          <t xml:space="preserve">ダチだ。何があっても守ってやる</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.delinquent.normal[1]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8671,14 +8671,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたけど…あいつ、やるじゃねぇか</t>
+          <t xml:space="preserve">…もう興味ねーよ</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8703,14 +8703,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合で最高の結果だ。文句ねぇだろ</t>
+          <t xml:space="preserve">目障りなんだよ…ぶっ潰してやる</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8720,12 +8720,12 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.delinquent.normal[1]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8735,14 +8735,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ…次は絶対ぶっ倒す</t>
+          <t xml:space="preserve">絶対ぶっ倒す。覚悟しろ</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8752,12 +8752,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.delinquent.normal[1]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8767,14 +8767,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったぜ。当然だろ</t>
+          <t xml:space="preserve">この勝負が全てだ。他はどうでもいい</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.delinquent.normal[1]</t>
+          <t xml:space="preserve">trust_above_75.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8799,14 +8799,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一本いくぞ、おら！</t>
+          <t xml:space="preserve">ここは私の場所だ。誰にも渡さねぇ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8816,12 +8816,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.delinquent.normal[1]</t>
+          <t xml:space="preserve">trust_below_20.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8831,14 +8831,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おい、最近の扱い何だよ…舐めてんのか</t>
+          <t xml:space="preserve">こんなとこ、もういられるか。出て行ってやる</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.delinquent.normal[1]</t>
+          <t xml:space="preserve">trust_below_35.normal.delinquent[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8863,14 +8863,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここも悪くねぇな。やる気出てきたぜ</t>
+          <t xml:space="preserve">ここ、ちゃんとしてんのかよ…不安になるぜ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8895,14 +8895,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">つるむの、結構楽しいんだよな</t>
+          <t xml:space="preserve">負けたけど…あいつ、やるじゃねぇか</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8927,14 +8927,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">顔が頭から離れねぇんだよ</t>
+          <t xml:space="preserve">最高の試合で最高の結果だ。文句ねぇだろ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-01.loss.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8959,14 +8959,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんで出してくれねぇんだよ…腕が鳴ってんのに</t>
+          <t xml:space="preserve">ちっ…次は絶対ぶっ倒す</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-01.win.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8991,14 +8991,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそ…体がついてこねぇ</t>
+          <t xml:space="preserve">勝ったぜ。当然だろ</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-02.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9023,14 +9023,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそが…何連敗してんだよ私は…</t>
+          <t xml:space="preserve">もう一本いくぞ、おら！</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-03.down.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9055,14 +9055,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちまくってるぜ。誰か止めてみろよ</t>
+          <t xml:space="preserve">おい、最近の扱い何だよ…舐めてんのか</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-03.up.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9087,14 +9087,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそ、いつまで寝てりゃいいんだよ…</t>
+          <t xml:space="preserve">ここも悪くねぇな。やる気出てきたぜ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-04.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9119,14 +9119,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー、いるな。それで？……別に</t>
+          <t xml:space="preserve">つるむの、結構楽しいんだよな</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-05.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9151,14 +9151,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チッ、終わっちまったか。まぁ上等だ</t>
+          <t xml:space="preserve">顔が頭から離れねぇんだよ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9168,29 +9168,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-06.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体ガタガタだけどよ。最後だ、引けるわけねえだろ</t>
+          <t xml:space="preserve">なんで出してくれねぇんだよ…腕が鳴ってんのに</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9200,29 +9200,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.normal[2]</t>
+          <t xml:space="preserve">GL-07.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">傷だらけ上等。この一戦、私が全部背負ってやる</t>
+          <t xml:space="preserve">くそ…体がついてこねぇ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9232,29 +9232,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-08.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰だ？ 何人来ようが、私がここで止めてやる</t>
+          <t xml:space="preserve">くそが…何連敗してんだよ私は…</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9264,29 +9264,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.normal[2]</t>
+          <t xml:space="preserve">GL-09.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリング、通れると思ってんのか。かかってこいよ</t>
+          <t xml:space="preserve">勝ちまくってるぜ。誰か止めてみろよ</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9296,29 +9296,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-10.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人潰した。…はぁ…まだ立ってんだよ。次、さっさと出てこいや</t>
+          <t xml:space="preserve">くそ、いつまで寝てりゃいいんだよ…</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9328,29 +9328,29 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.delinquent.normal[2]</t>
+          <t xml:space="preserve">GL-11.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わってねえぞ。息? 上がってるけど関係ねえ。次、来い</t>
+          <t xml:space="preserve">あー、いるな。それで？……別に</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9360,29 +9360,29 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人でもぎ取った勝ちだ。私一人の手柄じゃねえよ</t>
+          <t xml:space="preserve">チッ、終わっちまったか。まぁ上等だ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.normal[2]</t>
+          <t xml:space="preserve">preFinal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9407,14 +9407,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれたから、私はここにいる。それだけだろ</t>
+          <t xml:space="preserve">身体ガタガタだけどよ。最後だ、引けるわけねえだろ</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.delinquent.normal[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9439,14 +9439,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPったって、団体が負けてちゃ意味ねえよ。次は全員で勝つ</t>
+          <t xml:space="preserve">傷だらけ上等。この一戦、私が全部背負ってやる</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.delinquent.normal[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9471,14 +9471,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞はもらっとく。けど、次は優勝旗も一緒にだ</t>
+          <t xml:space="preserve">相手は誰だ？ 何人来ようが、私がここで止めてやる</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9488,12 +9488,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.delinquent.normal[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9503,14 +9503,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ようが関係ねえ。全員倒して、最後に立ってんのが私だ</t>
+          <t xml:space="preserve">このリング、通れると思ってんのか。かかってこいよ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.delinquent.normal[2]</t>
+          <t xml:space="preserve">survivor.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9535,14 +9535,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足ガクガクだけどよ、膝はつかなかった。それが全部だろ</t>
+          <t xml:space="preserve">一人潰した。…はぁ…まだ立ってんだよ。次、さっさと出てこいや</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.normal[1]</t>
+          <t xml:space="preserve">survivor.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9567,14 +9567,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テッペン獲ったぜ！ でもまだ上がある</t>
+          <t xml:space="preserve">まだ終わってねえぞ。息? 上がってるけど関係ねえ。次、来い</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.normal[2]</t>
+          <t xml:space="preserve">champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9599,14 +9599,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝…悪くねえな。もっと強くなってやる</t>
+          <t xml:space="preserve">三人でもぎ取った勝ちだ。私一人の手柄じゃねえよ</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9616,12 +9616,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.delinquent.normal[1]</t>
+          <t xml:space="preserve">champion.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9631,14 +9631,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…次は絶対負けねえ</t>
+          <t xml:space="preserve">仲間が繋いでくれたから、私はここにいる。それだけだろ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9648,12 +9648,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.delinquent.normal[2]</t>
+          <t xml:space="preserve">defiant.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9663,14 +9663,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなとこで終わってたまるか…</t>
+          <t xml:space="preserve">MVPったって、団体が負けてちゃ意味ねえよ。次は全員で勝つ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">defiant.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9695,14 +9695,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっし、一丁上がりだ。次もブチかます</t>
+          <t xml:space="preserve">この賞はもらっとく。けど、次は優勝旗も一緒にだ</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9712,12 +9712,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.delinquent.normal[2]</t>
+          <t xml:space="preserve">gauntlet.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9727,14 +9727,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ止まんねえぞ</t>
+          <t xml:space="preserve">何人来ようが関係ねえ。全員倒して、最後に立ってんのが私だ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">gauntlet.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9759,14 +9759,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあまあやれたな。次はもっと暴れてやるぜ</t>
+          <t xml:space="preserve">足ガクガクだけどよ、膝はつかなかった。それが全部だろ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.delinquent.normal[2]</t>
+          <t xml:space="preserve">champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9791,14 +9791,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悪くねえ結果だ</t>
+          <t xml:space="preserve">テッペン獲ったぜ！ でもまだ上がある</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.normal[1]</t>
+          <t xml:space="preserve">champion.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9823,14 +9823,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝だぜ。最後もぶっ潰してやる</t>
+          <t xml:space="preserve">優勝…悪くねえな。もっと強くなってやる</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.normal[2]</t>
+          <t xml:space="preserve">postLose.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9855,14 +9855,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たんだ。もう引けねえ</t>
+          <t xml:space="preserve">くそっ…次は絶対負けねえ</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.normal[1]</t>
+          <t xml:space="preserve">postLose.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9887,14 +9887,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっ潰す。それだけだ</t>
+          <t xml:space="preserve">こんなとこで終わってたまるか…</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.normal[2]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9919,14 +9919,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手とか関係ねえ。全力で行くだけだ</t>
+          <t xml:space="preserve">おっし、一丁上がりだ。次もブチかます</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.delinquent.normal[1]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9951,14 +9951,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おう、出てやるよ。覚悟しとけ</t>
+          <t xml:space="preserve">まだまだ止まんねえぞ</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.delinquent.normal[2]</t>
+          <t xml:space="preserve">postWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9983,14 +9983,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員まとめてかかって来いってんだ</t>
+          <t xml:space="preserve">まあまあやれたな。次はもっと暴れてやるぜ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10000,12 +10000,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">postWin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10015,14 +10015,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けねーぞ。かかってこい</t>
+          <t xml:space="preserve">悪くねえ結果だ</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10047,14 +10047,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうだ……！ これがウチの団体の力だ……！</t>
+          <t xml:space="preserve">決勝だぜ。最後もぶっ潰してやる</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">preFinal.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10079,14 +10079,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺん獲ったぞ……！ 見てたか……！</t>
+          <t xml:space="preserve">ここまで来たんだ。もう引けねえ</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10096,12 +10096,12 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10111,14 +10111,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おい、聞いたぜ？ 弱小団体がイキってるってな</t>
+          <t xml:space="preserve">ぶっ潰す。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10143,14 +10143,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ボコボコにしてやっから、覚悟しとけ</t>
+          <t xml:space="preserve">相手とか関係ねえ。全力で行くだけだ</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">summon.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10175,14 +10175,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、逃げやがった。ビビりが</t>
+          <t xml:space="preserve">おう、出てやるよ。覚悟しとけ</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">summon.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10207,14 +10207,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チキンかよ。次はねえぞ</t>
+          <t xml:space="preserve">全員まとめてかかって来いってんだ</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.normal[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10239,14 +10239,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…やられた…。次は絶対ぶっ潰す</t>
+          <t xml:space="preserve">今日は負けねーぞ。かかってこい</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.normal[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.delinquent.normal[2]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10271,14 +10271,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この借り…倍にして返してやるからな</t>
+          <t xml:space="preserve">どうだ……！ これがウチの団体の力だ……！</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10303,14 +10303,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうだ、これがウチの実力だ。舐めんなよ</t>
+          <t xml:space="preserve">てっぺん獲ったぞ……！ 見てたか……！</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.normal[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.delinquent.normal[2]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10335,14 +10335,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったぜ。ま、当然だけどな</t>
+          <t xml:space="preserve">おい、聞いたぜ？ 弱小団体がイキってるってな</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10352,12 +10352,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10367,14 +10367,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">舐めんなよ。うちの団体はこんなもんじゃねえ</t>
+          <t xml:space="preserve">ボコボコにしてやっから、覚悟しとけ</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10384,12 +10384,12 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10399,14 +10399,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったぜ。文句あるか？</t>
+          <t xml:space="preserve">はっ、逃げやがった。ビビりが</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[3]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[3]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10431,14 +10431,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽勝だぜ。次もかかってこいよ</t>
+          <t xml:space="preserve">チキンかよ。次はねえぞ</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.delinquent.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10448,29 +10448,29 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent.normal[1]</t>
+          <t xml:space="preserve">result_lose.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やってやったぜ！最高だ！</t>
+          <t xml:space="preserve">くそっ…やられた…。次は絶対ぶっ潰す</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10480,59 +10480,283 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">result_lose.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾われた借りは、リングで返す。それだけだ</t>
+          <t xml:space="preserve">この借り…倍にして返してやるからな</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">どうだ、これがウチの実力だ。舐めんなよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="40" customHeight="1">
+      <c r="A319" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.normal[2]</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.delinquent.normal[2]</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ったぜ。ま、当然だけどな</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="40" customHeight="1">
+      <c r="A320" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">舐めんなよ。うちの団体はこんなもんじゃねえ</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="40" customHeight="1">
+      <c r="A321" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[2]</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.normal[2]</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ったぜ。文句あるか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="40" customHeight="1">
+      <c r="A322" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[3]</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.normal[3]</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">楽勝だぜ。次もかかってこいよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="40" customHeight="1">
+      <c r="A323" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やってやったぜ！最高だ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="40" customHeight="1">
+      <c r="A324" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">拾われた借りは、リングで返す。それだけだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="40" customHeight="1">
+      <c r="A325" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.delinquent.normal[1]</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr" s="2">
+      <c r="B325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr" s="12">
+      <c r="D325" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr" s="2">
+      <c r="E325" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr" s="3">
+      <c r="F325" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">よく見つけたな。損はさせねーよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H318"/>
+  <autoFilter ref="A1:H325"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/ヤンキー×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/ヤンキー×ノーマル.xlsx
@@ -328,7 +328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H318"/>
+  <dimension ref="A1:H320"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -8774,7 +8774,7 @@
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-02-hostile.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8799,14 +8799,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一本いくぞ、おら！</t>
+          <t xml:space="preserve">次は絶対やってやる。絶対に…！</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-02-hostile.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8831,14 +8831,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おい、最近の扱い何だよ…舐めてんのか</t>
+          <t xml:space="preserve">あいつのことばっか考えてたら、バーベル落としそうになった</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-02.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8863,14 +8863,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここも悪くねぇな。やる気出てきたぜ</t>
+          <t xml:space="preserve">もう一本いくぞ、おら！</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-03.down.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8895,14 +8895,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">つるむの、結構楽しいんだよな</t>
+          <t xml:space="preserve">おい、最近の扱い何だよ…舐めてんのか</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-03.up.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8927,14 +8927,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">顔が頭から離れねぇんだよ</t>
+          <t xml:space="preserve">ここも悪くねぇな。やる気出てきたぜ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-04.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8959,14 +8959,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんで出してくれねぇんだよ…腕が鳴ってんのに</t>
+          <t xml:space="preserve">つるむの、結構楽しいんだよな</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-05.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8991,14 +8991,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそ…体がついてこねぇ</t>
+          <t xml:space="preserve">顔が頭から離れねぇんだよ</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-06.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9023,14 +9023,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそが…何連敗してんだよ私は…</t>
+          <t xml:space="preserve">なんで出してくれねぇんだよ…腕が鳴ってんのに</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-07.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9055,14 +9055,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちまくってるぜ。誰か止めてみろよ</t>
+          <t xml:space="preserve">くそ…体がついてこねぇ</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-08.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9087,14 +9087,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそ、いつまで寝てりゃいいんだよ…</t>
+          <t xml:space="preserve">くそが…何連敗してんだよ私は…</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-09.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9119,14 +9119,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー、いるな。それで？……別に</t>
+          <t xml:space="preserve">勝ちまくってるぜ。誰か止めてみろよ</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-10.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9151,14 +9151,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チッ、終わっちまったか。まぁ上等だ</t>
+          <t xml:space="preserve">くそ、いつまで寝てりゃいいんだよ…</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9168,29 +9168,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.normal[1]</t>
+          <t xml:space="preserve">GL-11.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体ガタガタだけどよ。最後だ、引けるわけねえだろ</t>
+          <t xml:space="preserve">あー、いるな。それで？……別に</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9200,29 +9200,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.normal[2]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">傷だらけ上等。この一戦、私が全部背負ってやる</t>
+          <t xml:space="preserve">チッ、終わっちまったか。まぁ上等だ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.normal[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9247,14 +9247,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰だ？ 何人来ようが、私がここで止めてやる</t>
+          <t xml:space="preserve">身体ガタガタだけどよ。最後だ、引けるわけねえだろ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.normal[2]</t>
+          <t xml:space="preserve">preFinal.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9279,14 +9279,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリング、通れると思ってんのか。かかってこいよ</t>
+          <t xml:space="preserve">傷だらけ上等。この一戦、私が全部背負ってやる</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.delinquent.normal[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9311,14 +9311,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人潰した。…はぁ…まだ立ってんだよ。次、さっさと出てこいや</t>
+          <t xml:space="preserve">相手は誰だ？ 何人来ようが、私がここで止めてやる</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.delinquent.normal[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9343,14 +9343,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わってねえぞ。息? 上がってるけど関係ねえ。次、来い</t>
+          <t xml:space="preserve">このリング、通れると思ってんのか。かかってこいよ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.normal[1]</t>
+          <t xml:space="preserve">survivor.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9375,14 +9375,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人でもぎ取った勝ちだ。私一人の手柄じゃねえよ</t>
+          <t xml:space="preserve">一人潰した。…はぁ…まだ立ってんだよ。次、さっさと出てこいや</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.normal[2]</t>
+          <t xml:space="preserve">survivor.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9407,14 +9407,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれたから、私はここにいる。それだけだろ</t>
+          <t xml:space="preserve">まだ終わってねえぞ。息? 上がってるけど関係ねえ。次、来い</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.delinquent.normal[1]</t>
+          <t xml:space="preserve">champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9439,14 +9439,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPったって、団体が負けてちゃ意味ねえよ。次は全員で勝つ</t>
+          <t xml:space="preserve">三人でもぎ取った勝ちだ。私一人の手柄じゃねえよ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.delinquent.normal[2]</t>
+          <t xml:space="preserve">champion.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9471,14 +9471,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞はもらっとく。けど、次は優勝旗も一緒にだ</t>
+          <t xml:space="preserve">仲間が繋いでくれたから、私はここにいる。それだけだろ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.delinquent.normal[1]</t>
+          <t xml:space="preserve">defiant.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9503,14 +9503,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ようが関係ねえ。全員倒して、最後に立ってんのが私だ</t>
+          <t xml:space="preserve">MVPったって、団体が負けてちゃ意味ねえよ。次は全員で勝つ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.delinquent.normal[2]</t>
+          <t xml:space="preserve">defiant.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9535,14 +9535,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足ガクガクだけどよ、膝はつかなかった。それが全部だろ</t>
+          <t xml:space="preserve">この賞はもらっとく。けど、次は優勝旗も一緒にだ</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.normal[1]</t>
+          <t xml:space="preserve">gauntlet.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9567,14 +9567,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テッペン獲ったぜ！ でもまだ上がある</t>
+          <t xml:space="preserve">何人来ようが関係ねえ。全員倒して、最後に立ってんのが私だ</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.delinquent.normal[2]</t>
+          <t xml:space="preserve">gauntlet.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9599,14 +9599,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝…悪くねえな。もっと強くなってやる</t>
+          <t xml:space="preserve">足ガクガクだけどよ、膝はつかなかった。それが全部だろ</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.delinquent.normal[1]</t>
+          <t xml:space="preserve">champion.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9631,14 +9631,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…次は絶対負けねえ</t>
+          <t xml:space="preserve">テッペン獲ったぜ！ でもまだ上がある</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.delinquent.normal[2]</t>
+          <t xml:space="preserve">champion.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9663,14 +9663,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなとこで終わってたまるか…</t>
+          <t xml:space="preserve">優勝…悪くねえな。もっと強くなってやる</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">postLose.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9695,14 +9695,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっし、一丁上がりだ。次もブチかます</t>
+          <t xml:space="preserve">くそっ…次は絶対負けねえ</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.delinquent.normal[2]</t>
+          <t xml:space="preserve">postLose.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9727,14 +9727,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ止まんねえぞ</t>
+          <t xml:space="preserve">こんなとこで終わってたまるか…</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.delinquent.normal[1]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9759,14 +9759,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあまあやれたな。次はもっと暴れてやるぜ</t>
+          <t xml:space="preserve">おっし、一丁上がりだ。次もブチかます</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.delinquent.normal[2]</t>
+          <t xml:space="preserve">postMatchWin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9791,14 +9791,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悪くねえ結果だ</t>
+          <t xml:space="preserve">まだまだ止まんねえぞ</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.normal[1]</t>
+          <t xml:space="preserve">postWin.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9823,14 +9823,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝だぜ。最後もぶっ潰してやる</t>
+          <t xml:space="preserve">まあまあやれたな。次はもっと暴れてやるぜ</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.delinquent.normal[2]</t>
+          <t xml:space="preserve">postWin.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9855,14 +9855,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たんだ。もう引けねえ</t>
+          <t xml:space="preserve">悪くねえ結果だ</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.normal[1]</t>
+          <t xml:space="preserve">preFinal.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9887,14 +9887,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっ潰す。それだけだ</t>
+          <t xml:space="preserve">決勝だぜ。最後もぶっ潰してやる</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.delinquent.normal[2]</t>
+          <t xml:space="preserve">preFinal.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9919,14 +9919,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手とか関係ねえ。全力で行くだけだ</t>
+          <t xml:space="preserve">ここまで来たんだ。もう引けねえ</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.delinquent.normal[1]</t>
+          <t xml:space="preserve">preMatch.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9951,14 +9951,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おう、出てやるよ。覚悟しとけ</t>
+          <t xml:space="preserve">ぶっ潰す。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.delinquent.normal[2]</t>
+          <t xml:space="preserve">preMatch.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9983,14 +9983,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員まとめてかかって来いってんだ</t>
+          <t xml:space="preserve">相手とか関係ねえ。全力で行くだけだ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10000,12 +10000,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">summon.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10015,14 +10015,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けねーぞ。かかってこい</t>
+          <t xml:space="preserve">おう、出てやるよ。覚悟しとけ</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">summon.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10047,14 +10047,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうだ……！ これがウチの団体の力だ……！</t>
+          <t xml:space="preserve">全員まとめてかかって来いってんだ</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.normal[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10079,14 +10079,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺん獲ったぞ……！ 見てたか……！</t>
+          <t xml:space="preserve">今日は負けねーぞ。かかってこい</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
@@ -10111,14 +10111,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おい、聞いたぜ？ 弱小団体がイキってるってな</t>
+          <t xml:space="preserve">どうだ……！ これがウチの団体の力だ……！</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.normal[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
@@ -10143,14 +10143,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ボコボコにしてやっから、覚悟しとけ</t>
+          <t xml:space="preserve">てっぺん獲ったぞ……！ 見てたか……！</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
@@ -10175,14 +10175,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、逃げやがった。ビビりが</t>
+          <t xml:space="preserve">おい、聞いたぜ？ 弱小団体がイキってるってな</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.normal[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
@@ -10207,14 +10207,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チキンかよ。次はねえぞ</t>
+          <t xml:space="preserve">ボコボコにしてやっから、覚悟しとけ</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.normal[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10239,14 +10239,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…やられた…。次は絶対ぶっ潰す</t>
+          <t xml:space="preserve">はっ、逃げやがった。ビビりが</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.normal[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.delinquent.normal[2]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10271,14 +10271,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この借り…倍にして返してやるからな</t>
+          <t xml:space="preserve">チキンかよ。次はねえぞ</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.delinquent.normal[1]</t>
+          <t xml:space="preserve">result_lose.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10303,14 +10303,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうだ、これがウチの実力だ。舐めんなよ</t>
+          <t xml:space="preserve">くそっ…やられた…。次は絶対ぶっ潰す</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.delinquent.normal[2]</t>
+          <t xml:space="preserve">result_lose.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10335,14 +10335,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったぜ。ま、当然だけどな</t>
+          <t xml:space="preserve">この借り…倍にして返してやるからな</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10352,12 +10352,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">result_win.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10367,14 +10367,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">舐めんなよ。うちの団体はこんなもんじゃねえ</t>
+          <t xml:space="preserve">どうだ、これがウチの実力だ。舐めんなよ</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10384,12 +10384,12 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[2]</t>
+          <t xml:space="preserve">result_win.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10399,14 +10399,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったぜ。文句あるか？</t>
+          <t xml:space="preserve">勝ったぜ。ま、当然だけどな</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[3]</t>
+          <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10431,14 +10431,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽勝だぜ。次もかかってこいよ</t>
+          <t xml:space="preserve">舐めんなよ。うちの団体はこんなもんじゃねえ</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.delinquent.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[2]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10448,29 +10448,29 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[2]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やってやったぜ！最高だ！</t>
+          <t xml:space="preserve">勝ったぜ。文句あるか？</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.delinquent.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.delinquent.normal[3]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10480,59 +10480,123 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent.normal[1]</t>
+          <t xml:space="preserve">delinquent.normal[3]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">拾われた借りは、リングで返す。それだけだ</t>
+          <t xml:space="preserve">楽勝だぜ。次もかかってこいよ</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やってやったぜ！最高だ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="40" customHeight="1">
+      <c r="A319" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent.normal[1]</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">拾われた借りは、リングで返す。それだけだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="40" customHeight="1">
+      <c r="A320" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.delinquent.normal[1]</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr" s="2">
+      <c r="B320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr" s="12">
+      <c r="D320" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">delinquent.normal[1]</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr" s="2">
+      <c r="E320" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr" s="3">
+      <c r="F320" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">よく見つけたな。損はさせねーよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H318"/>
+  <autoFilter ref="A1:H320"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/ヤンキー×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/ヤンキー×ノーマル.xlsx
@@ -2907,7 +2907,7 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あの人とやらせてください。</t>
+          <t xml:space="preserve">社長、三人であっちへ行かせてください。</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お願いがあるんすよ。あの人と当ててほしい。</t>
+          <t xml:space="preserve">お願いがあるんすよ。三人であの団体に当ててほしい。</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと引っかかってる相手がいる。組ませてください。</t>
+          <t xml:space="preserve">ずっと引っかかってる団体がある。三人で組ませてください。</t>
         </is>
       </c>
     </row>
